--- a/data/seed/portfolio/L-2024-8374/vypiska_2026-07_09.xlsx
+++ b/data/seed/portfolio/L-2024-8374/vypiska_2026-07_09.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J166"/>
+  <dimension ref="A1:J148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -542,301 +542,296 @@
       </c>
       <c r="C8" s="2" t="n"/>
       <c r="D8" s="2" t="n">
-        <v>116121000</v>
+        <v>20842000</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sharq Farm Savdo MChJ</t>
+          <t>Oltin Vodiy Trans Servis AJ</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>358401619</t>
+          <t>218152313</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>20208000122270147001</t>
+          <t>20208000145679461001</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MAHSULOT UCHUN TO'LOV, SHARTNOMA №174/26, QQS 12%</t>
+          <t>Оплата по с/ф №9305 за поставленный товар</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>398021000</v>
+        <v>302742000</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>46204</v>
+        <v>46209</v>
       </c>
       <c r="B9" t="n">
         <v>101</v>
       </c>
-      <c r="C9" s="2" t="n"/>
-      <c r="D9" s="2" t="n">
-        <v>12119000</v>
-      </c>
+      <c r="C9" s="2" t="n">
+        <v>20584000</v>
+      </c>
+      <c r="D9" s="2" t="n"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Zafar Trans Servis MChJ</t>
+          <t>Farg'ona Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>217207025</t>
+          <t>341394196</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>20208000750533919001</t>
+          <t>20208000239148343001</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №2080 от 01.07.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за товары согласно счет-фактуре №4737</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>410140000</v>
+        <v>282158000</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
-        <v>46206</v>
+        <v>46209</v>
       </c>
       <c r="B10" t="n">
         <v>102</v>
       </c>
-      <c r="C10" s="2" t="n"/>
-      <c r="D10" s="2" t="n">
-        <v>44337000</v>
-      </c>
+      <c r="C10" s="2" t="n">
+        <v>61077000</v>
+      </c>
+      <c r="D10" s="2" t="n"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Saodat Mehmonxona MChJ</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>391181523</t>
+          <t>Navbahor Bank ATB</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>20208000341456794001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №128/26, НДС 12%</t>
+          <t>Ish haqi to'lovi iyun 2026 (plastik kartalarga)</t>
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>454477000</v>
+        <v>221081000</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>46206</v>
+        <v>46210</v>
       </c>
       <c r="B11" t="n">
         <v>103</v>
       </c>
       <c r="C11" s="2" t="n"/>
       <c r="D11" s="2" t="n">
-        <v>9515000</v>
+        <v>11185000</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Angren Meva-Sabzavot MChJ</t>
+          <t>Oltin Vodiy Trans Servis AJ</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>253616498</t>
+          <t>218152313</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>20208000819652617001</t>
+          <t>20208000145679461001</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №9204 от 03.07.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за продукцию по договору №47/26, НДС 12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>463992000</v>
+        <v>232266000</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
-        <v>46206</v>
+        <v>46211</v>
       </c>
       <c r="B12" t="n">
         <v>104</v>
       </c>
       <c r="C12" s="2" t="n"/>
       <c r="D12" s="2" t="n">
-        <v>4557000</v>
+        <v>6930000</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Zafar Trans Servis MChJ</t>
+          <t>Oltin Vodiy Trans Servis AJ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>217207025</t>
+          <t>218152313</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>20208000750533919001</t>
+          <t>20208000145679461001</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №127/26 от 03.07.2026</t>
+          <t>Предоплата за товар по договору №219/26 от 08.07.2026</t>
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>468549000</v>
+        <v>239196000</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>46206</v>
+        <v>46211</v>
       </c>
       <c r="B13" t="n">
         <v>105</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>35362000</v>
+        <v>3604000</v>
       </c>
       <c r="D13" s="2" t="n"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sarbon Tikuv MChJ</t>
+          <t>Namangan Savdo MChJ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>249413941</t>
+          <t>238865009</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>20208000692391483001</t>
+          <t>20208000683302102001</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №192/26 от 03.07.2026, НДС 12%</t>
+          <t>Оплата за транспортные услуги по договору №278/26</t>
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>433187000</v>
+        <v>235592000</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
-        <v>46209</v>
+        <v>46211</v>
       </c>
       <c r="B14" t="n">
         <v>106</v>
       </c>
-      <c r="C14" s="2" t="n"/>
-      <c r="D14" s="2" t="n">
-        <v>30823000</v>
-      </c>
+      <c r="C14" s="2" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="D14" s="2" t="n"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Angren Meva-Sabzavot MChJ</t>
+          <t>Yangi Hayot Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>253616498</t>
+          <t>208026490</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>20208000819652617001</t>
+          <t>20208000194160103001</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №6538 за поставленный товар</t>
+          <t>Оплата за сырье по договору №201/26 от 08.07.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>464010000</v>
+        <v>231592000</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>46209</v>
+        <v>46211</v>
       </c>
       <c r="B15" t="n">
         <v>107</v>
       </c>
-      <c r="C15" s="2" t="n"/>
-      <c r="D15" s="2" t="n">
-        <v>13283000</v>
-      </c>
+      <c r="C15" s="2" t="n">
+        <v>9361000</v>
+      </c>
+      <c r="D15" s="2" t="n"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Saodat Mehmonxona MChJ</t>
+          <t>Namangan Savdo MChJ</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>391181523</t>
+          <t>238865009</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>20208000341456794001</t>
+          <t>20208000683302102001</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -846,37 +841,37 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГ. №263/26 ОТ 06.07.2026</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №148/26</t>
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>477293000</v>
+        <v>222231000</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
-        <v>46209</v>
+        <v>46212</v>
       </c>
       <c r="B16" t="n">
         <v>108</v>
       </c>
       <c r="C16" s="2" t="n"/>
       <c r="D16" s="2" t="n">
-        <v>10500000</v>
+        <v>16978000</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Saodat Mehmonxona MChJ</t>
+          <t>Ziyo Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>391181523</t>
+          <t>340161921</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>20208000341456794001</t>
+          <t>20208000227014773001</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -886,272 +881,277 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №8036 за поставленный товар</t>
+          <t>Оплата по с/ф №4160 за поставленный товар</t>
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>487793000</v>
+        <v>239209000</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>46209</v>
+        <v>46212</v>
       </c>
       <c r="B17" t="n">
         <v>109</v>
       </c>
-      <c r="C17" s="2" t="n"/>
-      <c r="D17" s="2" t="n">
-        <v>4113000</v>
-      </c>
+      <c r="C17" s="2" t="n">
+        <v>6470000</v>
+      </c>
+      <c r="D17" s="2" t="n"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Angren Meva-Sabzavot MChJ</t>
+          <t>Saodat Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>253616498</t>
+          <t>380705809</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>20208000819652617001</t>
+          <t>20208000721145870001</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №5238</t>
+          <t>Арендная плата за июль 2026 г. по дог. №81/24</t>
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>491906000</v>
+        <v>232739000</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>46209</v>
+        <v>46213</v>
       </c>
       <c r="B18" t="n">
         <v>110</v>
       </c>
-      <c r="C18" s="2" t="n"/>
-      <c r="D18" s="2" t="n">
-        <v>4038000</v>
-      </c>
+      <c r="C18" s="2" t="n">
+        <v>3894000</v>
+      </c>
+      <c r="D18" s="2" t="n"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Angren Meva-Sabzavot MChJ</t>
+          <t>Yangi Hayot Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>253616498</t>
+          <t>208026490</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>20208000819652617001</t>
+          <t>20208000194160103001</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №200/26, НДС 12%</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №7/26, QQS bilan</t>
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>495944000</v>
+        <v>228845000</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>46209</v>
+        <v>46216</v>
       </c>
       <c r="B19" t="n">
         <v>111</v>
       </c>
-      <c r="C19" s="2" t="n">
-        <v>55157000</v>
-      </c>
-      <c r="D19" s="2" t="n"/>
+      <c r="C19" s="2" t="n"/>
+      <c r="D19" s="2" t="n">
+        <v>9755000</v>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Gulshan Qurilish MChJ</t>
+          <t>Ziyo Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>261605721</t>
+          <t>340161921</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>20208000392064893001</t>
+          <t>20208000227014773001</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №257/26</t>
+          <t>Оплата по счет-фактуре №4827 за поставленный товар</t>
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>440787000</v>
+        <v>238600000</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>46209</v>
+        <v>46216</v>
       </c>
       <c r="B20" t="n">
         <v>112</v>
       </c>
-      <c r="C20" s="2" t="n">
-        <v>55297000</v>
-      </c>
-      <c r="D20" s="2" t="n"/>
+      <c r="C20" s="2" t="n"/>
+      <c r="D20" s="2" t="n">
+        <v>5218000</v>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sarbon Tikuv MChJ</t>
+          <t>Bog'ishamol Poligraf MChJ</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>249413941</t>
+          <t>261649818</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>20208000692391483001</t>
+          <t>20208000965261771001</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №6086</t>
+          <t>Оплата за продукцию по договору №154/26, НДС 12%</t>
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>385490000</v>
+        <v>243818000</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>46209</v>
+        <v>46216</v>
       </c>
       <c r="B21" t="n">
         <v>113</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>61077000</v>
+        <v>4167000</v>
       </c>
       <c r="D21" s="2" t="n"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Navbahor Bank ATB</t>
+          <t>Farg'ona Avto Ehtiyot MChJ</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>341394196</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000239148343001</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Заработная плата за июнь 2026 г. (перечисление на пластиковые карты)</t>
+          <t>Оплата за товары согласно счет-фактуре №9922</t>
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>324413000</v>
+        <v>239651000</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
-        <v>46210</v>
+        <v>46216</v>
       </c>
       <c r="B22" t="n">
         <v>114</v>
       </c>
-      <c r="C22" s="2" t="n"/>
-      <c r="D22" s="2" t="n">
-        <v>37300000</v>
-      </c>
+      <c r="C22" s="2" t="n">
+        <v>15477000</v>
+      </c>
+      <c r="D22" s="2" t="n"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Angren Meva-Sabzavot MChJ</t>
+          <t>Farg'ona Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>253616498</t>
+          <t>341394196</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>20208000819652617001</t>
+          <t>20208000239148343001</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №14/26 от 07.07.2026</t>
+          <t>Оплата за упаковочные материалы, с/ф №638</t>
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>361713000</v>
+        <v>224174000</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>46210</v>
+        <v>46217</v>
       </c>
       <c r="B23" t="n">
         <v>115</v>
       </c>
       <c r="C23" s="2" t="n"/>
       <c r="D23" s="2" t="n">
-        <v>20683000</v>
+        <v>5166000</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sharq Farm Savdo MChJ</t>
+          <t>Bog'ishamol Poligraf MChJ</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>358401619</t>
+          <t>261649818</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>20208000122270147001</t>
+          <t>20208000965261771001</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1161,117 +1161,117 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №143/26, НДС 12%</t>
+          <t>Оплата за продукцию по договору №113/26, НДС 12%</t>
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>382396000</v>
+        <v>229340000</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
-        <v>46210</v>
+        <v>46217</v>
       </c>
       <c r="B24" t="n">
         <v>116</v>
       </c>
-      <c r="C24" s="2" t="n"/>
-      <c r="D24" s="2" t="n">
-        <v>8532000</v>
-      </c>
+      <c r="C24" s="2" t="n">
+        <v>8329000</v>
+      </c>
+      <c r="D24" s="2" t="n"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Zafar Trans Servis MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>217207025</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>20208000750533919001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №130/26 от 07.07.2026</t>
+          <t>Уплата социального налога за июнь</t>
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>390928000</v>
+        <v>221011000</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>46210</v>
+        <v>46217</v>
       </c>
       <c r="B25" t="n">
         <v>117</v>
       </c>
-      <c r="C25" s="2" t="n"/>
-      <c r="D25" s="2" t="n">
-        <v>3723000</v>
-      </c>
+      <c r="C25" s="2" t="n">
+        <v>8329000</v>
+      </c>
+      <c r="D25" s="2" t="n"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Angren Meva-Sabzavot MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>253616498</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>20208000819652617001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №8303 за поставленный товар</t>
+          <t>Налог на доходы физических лиц за июнь 2026 г.</t>
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>394651000</v>
+        <v>212682000</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
-        <v>46211</v>
+        <v>46218</v>
       </c>
       <c r="B26" t="n">
         <v>118</v>
       </c>
-      <c r="C26" s="2" t="n">
-        <v>6470000</v>
-      </c>
-      <c r="D26" s="2" t="n"/>
+      <c r="C26" s="2" t="n"/>
+      <c r="D26" s="2" t="n">
+        <v>4681000</v>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Yulduz Qurilish MChJ</t>
+          <t>Nihol Plastik XK</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>324719468</t>
+          <t>318371553</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>20208000817375960001</t>
+          <t>20208000753902296001</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1281,197 +1281,197 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Ijara haqi iyul oyi uchun, shartnoma №32/22</t>
+          <t>Shartnoma №49/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>388181000</v>
+        <v>217363000</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>46211</v>
+        <v>46218</v>
       </c>
       <c r="B27" t="n">
         <v>119</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>124999000</v>
+        <v>12377000</v>
       </c>
       <c r="D27" s="2" t="n"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sarbon Tikuv MChJ</t>
+          <t>Yangi Hayot Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>249413941</t>
+          <t>208026490</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>20208000692391483001</t>
+          <t>20208000194160103001</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №87/26, QQS bilan</t>
+          <t>Оплата за транспортные услуи по договору №96/26</t>
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>263182000</v>
+        <v>204986000</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
-        <v>46212</v>
+        <v>46219</v>
       </c>
       <c r="B28" t="n">
         <v>120</v>
       </c>
       <c r="C28" s="2" t="n"/>
       <c r="D28" s="2" t="n">
-        <v>9422000</v>
+        <v>10511000</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Angren Meva-Sabzavot MChJ</t>
+          <t>Bog'ishamol Poligraf MChJ</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>253616498</t>
+          <t>261649818</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>20208000819652617001</t>
+          <t>20208000965261771001</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №2825 за поставленный товар</t>
+          <t>Оплата за продукцию по договору №86/26, НДС 12%</t>
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>272604000</v>
+        <v>215497000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>46216</v>
+        <v>46219</v>
       </c>
       <c r="B29" t="n">
         <v>121</v>
       </c>
       <c r="C29" s="2" t="n"/>
       <c r="D29" s="2" t="n">
-        <v>155051000</v>
+        <v>4375000</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Angren Meva-Sabzavot MChJ</t>
+          <t>Bog'ishamol Poligraf MChJ</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>253616498</t>
+          <t>261649818</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>20208000819652617001</t>
+          <t>20208000965261771001</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №3639 от 13.07.2026, в т.ч. НДС 12%</t>
+          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГ. №102/26 ОТ 16.07.2026</t>
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>427655000</v>
+        <v>219872000</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
-        <v>46216</v>
+        <v>46219</v>
       </c>
       <c r="B30" t="n">
         <v>122</v>
       </c>
-      <c r="C30" s="2" t="n"/>
-      <c r="D30" s="2" t="n">
-        <v>84789000</v>
-      </c>
+      <c r="C30" s="2" t="n">
+        <v>12055000</v>
+      </c>
+      <c r="D30" s="2" t="n"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ziyo Qog'oz MChJ</t>
+          <t>Yangi Hayot Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>337092554</t>
+          <t>208026490</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>20208000093660809001</t>
+          <t>20208000194160103001</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №281/26 от 13.07.2026</t>
+          <t>Оплата за транспортные услуги по договору №223/26</t>
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>512444000</v>
+        <v>207817000</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>46216</v>
+        <v>46220</v>
       </c>
       <c r="B31" t="n">
         <v>123</v>
       </c>
-      <c r="C31" s="2" t="n"/>
-      <c r="D31" s="2" t="n">
-        <v>30011000</v>
-      </c>
+      <c r="C31" s="2" t="n">
+        <v>26331000</v>
+      </c>
+      <c r="D31" s="2" t="n"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sharq Farm Savdo MChJ</t>
+          <t>Yangi Hayot Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>358401619</t>
+          <t>208026490</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>20208000122270147001</t>
+          <t>20208000194160103001</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1481,597 +1481,592 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №209/26, НДС 12%</t>
+          <t>Оплата за товары согласно счет-фактуре №4714</t>
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>542455000</v>
+        <v>181486000</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
-        <v>46216</v>
+        <v>46223</v>
       </c>
       <c r="B32" t="n">
         <v>124</v>
       </c>
       <c r="C32" s="2" t="n"/>
       <c r="D32" s="2" t="n">
-        <v>13613000</v>
+        <v>14743000</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Angren Meva-Sabzavot MChJ</t>
+          <t>Ziyo Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>253616498</t>
+          <t>340161921</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>20208000819652617001</t>
+          <t>20208000227014773001</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №247/26 от 13.07.2026</t>
+          <t>ОПЛАТА ЗА ТОВАР ПО СЧЕТ-ФАКТУРЕ №7749 ОТ 20.07.2026, В Т.Ч. НДС 12%</t>
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>556068000</v>
+        <v>196229000</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>46216</v>
+        <v>46223</v>
       </c>
       <c r="B33" t="n">
         <v>125</v>
       </c>
-      <c r="C33" s="2" t="n"/>
-      <c r="D33" s="2" t="n">
-        <v>12661000</v>
-      </c>
+      <c r="C33" s="2" t="n">
+        <v>9345000</v>
+      </c>
+      <c r="D33" s="2" t="n"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Xiva Meva-Sabzavot MChJ</t>
+          <t>Yangi Hayot Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>361080264</t>
+          <t>208026490</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>20208000031941601001</t>
+          <t>20208000194160103001</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №6922 за поставленный товар</t>
+          <t>Оплата за упаковочные материалы, с/ф №8457</t>
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>568729000</v>
+        <v>186884000</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
-        <v>46216</v>
+        <v>46223</v>
       </c>
       <c r="B34" t="n">
         <v>126</v>
       </c>
-      <c r="C34" s="2" t="n"/>
-      <c r="D34" s="2" t="n">
-        <v>12200000</v>
-      </c>
+      <c r="C34" s="2" t="n">
+        <v>46182000</v>
+      </c>
+      <c r="D34" s="2" t="n"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Qarshi Qog'oz AJ</t>
+          <t>Yangi Hayot Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>268883284</t>
+          <t>208026490</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>20208000822335239001</t>
+          <t>20208000194160103001</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №33/26 от 13.07.2026</t>
+          <t>Оплата за транспортные услуги по договору №134/26</t>
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>580929000</v>
+        <v>140702000</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>46216</v>
+        <v>46223</v>
       </c>
       <c r="B35" t="n">
         <v>127</v>
       </c>
-      <c r="C35" s="2" t="n"/>
-      <c r="D35" s="2" t="n">
-        <v>10499000</v>
-      </c>
+      <c r="C35" s="2" t="n">
+        <v>569068000</v>
+      </c>
+      <c r="D35" s="2" t="n"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Nukus Oziq-ovqat Savdo MChJ</t>
+          <t>Yangi Hayot Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>316189013</t>
+          <t>208026490</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>20208000860801121001</t>
+          <t>20208000194160103001</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №59/26, НДС 12%</t>
+          <t>Предоплата за материалы по договору №67/26</t>
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>591428000</v>
+        <v>-428366000</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
-        <v>46216</v>
+        <v>46225</v>
       </c>
       <c r="B36" t="n">
         <v>128</v>
       </c>
       <c r="C36" s="2" t="n"/>
       <c r="D36" s="2" t="n">
-        <v>9540000</v>
+        <v>27718000</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Angren Meva-Sabzavot MChJ</t>
+          <t>Shahrisabz Farm Savdo XK</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>253616498</t>
+          <t>388328458</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>20208000819652617001</t>
+          <t>20208000233523997001</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №654 за поставленный товар</t>
+          <t>Оплата по с/ф №7648 за поставленный товар</t>
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>600968000</v>
+        <v>-400648000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>46216</v>
+        <v>46225</v>
       </c>
       <c r="B37" t="n">
         <v>129</v>
       </c>
-      <c r="C37" s="2" t="n"/>
-      <c r="D37" s="2" t="n">
-        <v>5262000</v>
-      </c>
+      <c r="C37" s="2" t="n">
+        <v>3763000</v>
+      </c>
+      <c r="D37" s="2" t="n"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Angren Meva-Sabzavot MChJ</t>
+          <t>Yangi Hayot Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>253616498</t>
+          <t>208026490</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>20208000819652617001</t>
+          <t>20208000194160103001</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №210/26, НДС 12%</t>
+          <t>Оплата за транспортные услуги по дог. №203/26</t>
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>606230000</v>
+        <v>-404411000</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="n">
-        <v>46216</v>
+        <v>46226</v>
       </c>
       <c r="B38" t="n">
         <v>130</v>
       </c>
-      <c r="C38" s="2" t="n"/>
-      <c r="D38" s="2" t="n">
-        <v>4899000</v>
-      </c>
+      <c r="C38" s="2" t="n">
+        <v>4044000</v>
+      </c>
+      <c r="D38" s="2" t="n"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Saodat Mehmonxona MChJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>391181523</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>20208000341456794001</t>
+          <t>20208000165844298001</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Shartnoma №214/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за электроэнергию согласно счету</t>
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>611129000</v>
+        <v>-408455000</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>46216</v>
+        <v>46226</v>
       </c>
       <c r="B39" t="n">
         <v>131</v>
       </c>
-      <c r="C39" s="2" t="n"/>
-      <c r="D39" s="2" t="n">
-        <v>4371000</v>
-      </c>
+      <c r="C39" s="2" t="n">
+        <v>5022000</v>
+      </c>
+      <c r="D39" s="2" t="n"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Sharq Farm Savdo MChJ</t>
+          <t>Nurafshon Yog'och AJ</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>358401619</t>
+          <t>328909975</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>20208000122270147001</t>
+          <t>20208000034535471001</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №15/26, QQS 12%</t>
+          <t>Оплата за сырье по дог. №291/26 от 23.07.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>615500000</v>
+        <v>-413477000</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="n">
-        <v>46216</v>
+        <v>46226</v>
       </c>
       <c r="B40" t="n">
         <v>132</v>
       </c>
       <c r="C40" s="2" t="n">
-        <v>57212000</v>
+        <v>10826000</v>
       </c>
       <c r="D40" s="2" t="n"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Sarbon Tikuv MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>249413941</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>20208000692391483001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №148/26</t>
+          <t>Qo'shilgan qiymat solig'i iyun oyi</t>
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>558288000</v>
+        <v>-424303000</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
-        <v>46218</v>
+        <v>46228</v>
       </c>
       <c r="B41" t="n">
         <v>133</v>
       </c>
       <c r="C41" s="2" t="n">
-        <v>8329000</v>
+        <v>44100000</v>
       </c>
       <c r="D41" s="2" t="n"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>201122905</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2024-8374)</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>16307000381312376417</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Уплата социального налога за июнь</t>
+          <t>Kredit shartnomasi L-2024-8374 bo'yicha navbatdagi to'lov (07.2026)</t>
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>549959000</v>
+        <v>-468403000</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="n">
-        <v>46218</v>
+        <v>46230</v>
       </c>
       <c r="B42" t="n">
         <v>134</v>
       </c>
-      <c r="C42" s="2" t="n">
-        <v>8329000</v>
-      </c>
-      <c r="D42" s="2" t="n"/>
+      <c r="C42" s="2" t="n"/>
+      <c r="D42" s="2" t="n">
+        <v>28282000</v>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Bog'ishamol Poligraf MChJ</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>261649818</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000965261771001</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>JShDS iyun oyi uchun</t>
+          <t>Tovar ucun to'lov, h/f №7217 27.07.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>541630000</v>
+        <v>-440121000</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="n">
-        <v>46219</v>
+        <v>46230</v>
       </c>
       <c r="B43" t="n">
         <v>135</v>
       </c>
-      <c r="C43" s="2" t="n"/>
-      <c r="D43" s="2" t="n">
-        <v>25292000</v>
-      </c>
+      <c r="C43" s="2" t="n">
+        <v>13792000</v>
+      </c>
+      <c r="D43" s="2" t="n"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Angren Meva-Sabzavot MChJ</t>
+          <t>Namangan Savdo MChJ</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>253616498</t>
+          <t>238865009</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>20208000819652617001</t>
+          <t>20208000683302102001</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №2963 за поставленный товар</t>
+          <t>TOVARLAR UCHUN TO'LOV H/F №4978</t>
         </is>
       </c>
       <c r="J43" s="2" t="n">
-        <v>566922000</v>
+        <v>-453913000</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="n">
-        <v>46219</v>
+        <v>46231</v>
       </c>
       <c r="B44" t="n">
         <v>136</v>
       </c>
       <c r="C44" s="2" t="n"/>
       <c r="D44" s="2" t="n">
-        <v>17922000</v>
+        <v>96397000</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Angren Meva-Sabzavot MChJ</t>
+          <t>Bog'ishamol Poligraf MChJ</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>253616498</t>
+          <t>261649818</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>20208000819652617001</t>
+          <t>20208000965261771001</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №223/26, QQS 12%</t>
+          <t>Оплата по счет-фактуре №4435 за поставленный товар</t>
         </is>
       </c>
       <c r="J44" s="2" t="n">
-        <v>584844000</v>
+        <v>-357516000</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="n">
-        <v>46219</v>
+        <v>46231</v>
       </c>
       <c r="B45" t="n">
         <v>137</v>
       </c>
       <c r="C45" s="2" t="n"/>
       <c r="D45" s="2" t="n">
-        <v>11060000</v>
+        <v>51350000</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Angren Meva-Sabzavot MChJ</t>
+          <t>Bog'ishamol Poligraf MChJ</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>253616498</t>
+          <t>261649818</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>20208000819652617001</t>
+          <t>20208000965261771001</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №4553 за посталенный товар</t>
+          <t>Оплата за товар по счет-фактуре №1018 от 28.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>595904000</v>
+        <v>-306166000</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="n">
-        <v>46219</v>
+        <v>46232</v>
       </c>
       <c r="B46" t="n">
         <v>138</v>
       </c>
-      <c r="C46" s="2" t="n">
-        <v>44782000</v>
-      </c>
-      <c r="D46" s="2" t="n"/>
+      <c r="C46" s="2" t="n"/>
+      <c r="D46" s="2" t="n">
+        <v>521482000</v>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Andijon Un Mahsulotlari MChJ</t>
+          <t>Bog'ishamol Poligraf MChJ</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>291057367</t>
+          <t>261649818</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>20208000362550229001</t>
+          <t>20208000965261771001</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2081,37 +2076,37 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №261/26</t>
+          <t>Предоплата за товар по договору №140/26 от 29.07.2026</t>
         </is>
       </c>
       <c r="J46" s="2" t="n">
-        <v>551122000</v>
+        <v>215316000</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="n">
-        <v>46220</v>
+        <v>46232</v>
       </c>
       <c r="B47" t="n">
         <v>139</v>
       </c>
       <c r="C47" s="2" t="n">
-        <v>37379000</v>
+        <v>4939000</v>
       </c>
       <c r="D47" s="2" t="n"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Durdona Mebel AJ</t>
+          <t>Farg'ona Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>246657965</t>
+          <t>341394196</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>20208000591929530001</t>
+          <t>20208000239148343001</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2121,117 +2116,112 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №9015</t>
+          <t>Оплата за упаковочные материалы, с/ф №5992</t>
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>513743000</v>
+        <v>210377000</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="n">
-        <v>46223</v>
+        <v>46233</v>
       </c>
       <c r="B48" t="n">
         <v>140</v>
       </c>
       <c r="C48" s="2" t="n"/>
       <c r="D48" s="2" t="n">
-        <v>25199000</v>
+        <v>45629000</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Angren Meva-Sabzavot MChJ</t>
+          <t>Nihol Non MChJ</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>253616498</t>
+          <t>365496405</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>20208000819652617001</t>
+          <t>20208000922502059001</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №240/26, НДС 12%</t>
+          <t>Оплата за товар по счет-фактуре №9633 от 30.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>538942000</v>
+        <v>256006000</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="n">
-        <v>46223</v>
+        <v>46234</v>
       </c>
       <c r="B49" t="n">
         <v>141</v>
       </c>
-      <c r="C49" s="2" t="n">
-        <v>58239000</v>
-      </c>
-      <c r="D49" s="2" t="n"/>
+      <c r="C49" s="2" t="n"/>
+      <c r="D49" s="2" t="n">
+        <v>20931000</v>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Durdona Mebel AJ</t>
+          <t>Ziyo Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>246657965</t>
+          <t>340161921</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>20208000591929530001</t>
+          <t>20208000227014773001</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №258/26</t>
+          <t>Оплата за продукцию по договору №107/26, НДС 12%</t>
         </is>
       </c>
       <c r="J49" s="2" t="n">
-        <v>480703000</v>
+        <v>276937000</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="n">
-        <v>46224</v>
+        <v>46234</v>
       </c>
       <c r="B50" t="n">
         <v>142</v>
       </c>
-      <c r="C50" s="2" t="n"/>
-      <c r="D50" s="2" t="n">
-        <v>35208000</v>
-      </c>
+      <c r="C50" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D50" s="2" t="n"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Angren Meva-Sabzavot MChJ</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>253616498</t>
+          <t>Navbahor Bank ATB</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>20208000819652617001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2241,117 +2231,117 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №3467 за поставленный товар</t>
+          <t>Hisob-kassa xizmati uchun haq</t>
         </is>
       </c>
       <c r="J50" s="2" t="n">
-        <v>515911000</v>
+        <v>276637000</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="n">
-        <v>46224</v>
+        <v>46237</v>
       </c>
       <c r="B51" t="n">
         <v>143</v>
       </c>
       <c r="C51" s="2" t="n"/>
       <c r="D51" s="2" t="n">
-        <v>21839000</v>
+        <v>16112000</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Angren Meva-Sabzavot MChJ</t>
+          <t>Ziyo Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>253616498</t>
+          <t>340161921</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>20208000819652617001</t>
+          <t>20208000227014773001</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №2538 от 21.07.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за твар по с/ф №2474 от 03.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J51" s="2" t="n">
-        <v>537750000</v>
+        <v>292749000</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="n">
-        <v>46225</v>
+        <v>46237</v>
       </c>
       <c r="B52" t="n">
         <v>144</v>
       </c>
-      <c r="C52" s="2" t="n">
-        <v>10839000</v>
-      </c>
-      <c r="D52" s="2" t="n"/>
+      <c r="C52" s="2" t="n"/>
+      <c r="D52" s="2" t="n">
+        <v>12809000</v>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Oltin Vodiy Trans Servis AJ</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>218152313</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000145679461001</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>НДС за июнь 2026 г.</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №7067</t>
         </is>
       </c>
       <c r="J52" s="2" t="n">
-        <v>526911000</v>
+        <v>305558000</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="n">
-        <v>46226</v>
+        <v>46237</v>
       </c>
       <c r="B53" t="n">
         <v>145</v>
       </c>
       <c r="C53" s="2" t="n"/>
       <c r="D53" s="2" t="n">
-        <v>22492000</v>
+        <v>6326000</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Saodat Mehmonxona MChJ</t>
+          <t>Shahrisabz Farm Savdo XK</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>391181523</t>
+          <t>388328458</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>20208000341456794001</t>
+          <t>20208000233523997001</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2361,77 +2351,77 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №70/26, НДС 12%</t>
+          <t>Предоплата за товар по дог. №136/26 от 03.08.2026</t>
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>549403000</v>
+        <v>311884000</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="n">
-        <v>46226</v>
+        <v>46237</v>
       </c>
       <c r="B54" t="n">
         <v>146</v>
       </c>
-      <c r="C54" s="2" t="n"/>
-      <c r="D54" s="2" t="n">
-        <v>8632000</v>
-      </c>
+      <c r="C54" s="2" t="n">
+        <v>94403000</v>
+      </c>
+      <c r="D54" s="2" t="n"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Angren Meva-Sabzavot MChJ</t>
+          <t>Yangi Hayot Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>253616498</t>
+          <t>208026490</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>20208000819652617001</t>
+          <t>20208000194160103001</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №130/26, НДС 12%</t>
+          <t>Предоплата за материалы по договору №285/26</t>
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>558035000</v>
+        <v>217481000</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="n">
-        <v>46226</v>
+        <v>46238</v>
       </c>
       <c r="B55" t="n">
         <v>147</v>
       </c>
       <c r="C55" s="2" t="n"/>
       <c r="D55" s="2" t="n">
-        <v>4396000</v>
+        <v>33830000</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Sharq Farm Savdo MChJ</t>
+          <t>Ziyo Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>358401619</t>
+          <t>340161921</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>20208000122270147001</t>
+          <t>20208000227014773001</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -2441,37 +2431,37 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №143/26 от 23.07.2026</t>
+          <t>Предоплата за товар по договору №276/26 от 04.08.2026</t>
         </is>
       </c>
       <c r="J55" s="2" t="n">
-        <v>562431000</v>
+        <v>251311000</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="n">
-        <v>46227</v>
+        <v>46238</v>
       </c>
       <c r="B56" t="n">
         <v>148</v>
       </c>
-      <c r="C56" s="2" t="n"/>
-      <c r="D56" s="2" t="n">
-        <v>8117000</v>
-      </c>
+      <c r="C56" s="2" t="n">
+        <v>43249000</v>
+      </c>
+      <c r="D56" s="2" t="n"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Sharq Farm Savdo MChJ</t>
+          <t>Farg'ona Agro Servis MChJ</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>358401619</t>
+          <t>357933970</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>20208000122270147001</t>
+          <t>20208000481223981001</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -2481,192 +2471,192 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №63/26, НДС 12%</t>
+          <t>Оплата за транспортные услуги по договору №218/26</t>
         </is>
       </c>
       <c r="J56" s="2" t="n">
-        <v>570548000</v>
+        <v>208062000</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="n">
-        <v>46227</v>
+        <v>46240</v>
       </c>
       <c r="B57" t="n">
         <v>149</v>
       </c>
       <c r="C57" s="2" t="n">
-        <v>15752000</v>
+        <v>14369000</v>
       </c>
       <c r="D57" s="2" t="n"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Gulshan Qurilish MChJ</t>
+          <t>Yangi Hayot Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>261605721</t>
+          <t>208026490</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>20208000392064893001</t>
+          <t>20208000194160103001</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №1912</t>
+          <t>Оплата за упаковочные материалы, с/ф №6772</t>
         </is>
       </c>
       <c r="J57" s="2" t="n">
-        <v>554796000</v>
+        <v>193693000</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="n">
-        <v>46227</v>
+        <v>46240</v>
       </c>
       <c r="B58" t="n">
         <v>150</v>
       </c>
       <c r="C58" s="2" t="n">
-        <v>109135000</v>
+        <v>64816000</v>
       </c>
       <c r="D58" s="2" t="n"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Andijon Un Mahsulotlari MChJ</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>291057367</t>
+          <t>Navbahor Bank ATB</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>20208000362550229001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №5598</t>
+          <t>Ish haqi to'lovi iyul 2026 (plastik kartalarga)</t>
         </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>445661000</v>
+        <v>128877000</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="n">
-        <v>46228</v>
+        <v>46244</v>
       </c>
       <c r="B59" t="n">
         <v>151</v>
       </c>
-      <c r="C59" s="2" t="n">
-        <v>44100000</v>
-      </c>
-      <c r="D59" s="2" t="n"/>
+      <c r="C59" s="2" t="n"/>
+      <c r="D59" s="2" t="n">
+        <v>131079000</v>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2024-8374)</t>
+          <t>Bog'ishamol Poligraf MChJ</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>261649818</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>16307000381312376417</t>
+          <t>20208000965261771001</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2024-8374 bo'yicha navbatdagi to'lov (07.2026)</t>
+          <t>Tovar uchun to'lov, hisob-faktura №6850 10.08.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J59" s="2" t="n">
-        <v>401561000</v>
+        <v>259956000</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="n">
-        <v>46230</v>
+        <v>46244</v>
       </c>
       <c r="B60" t="n">
         <v>152</v>
       </c>
       <c r="C60" s="2" t="n"/>
       <c r="D60" s="2" t="n">
-        <v>5690000</v>
+        <v>34202000</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Angren Meva-Sabzavot MChJ</t>
+          <t>Nihol Non MChJ</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>253616498</t>
+          <t>365496405</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>20208000819652617001</t>
+          <t>20208000922502059001</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №1083 от 27.07.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за товар по счет-фактуре №8052 от 10.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J60" s="2" t="n">
-        <v>407251000</v>
+        <v>294158000</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="n">
-        <v>46230</v>
+        <v>46244</v>
       </c>
       <c r="B61" t="n">
         <v>153</v>
       </c>
       <c r="C61" s="2" t="n"/>
       <c r="D61" s="2" t="n">
-        <v>4028000</v>
+        <v>19846000</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Sharq Farm Savdo MChJ</t>
+          <t>Ziyo Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>358401619</t>
+          <t>340161921</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>20208000122270147001</t>
+          <t>20208000227014773001</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -2676,352 +2666,357 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГОВОРУ №29/26, НДС 12%</t>
+          <t>Оплата по счет-фактуре №8197 за поставленный товар</t>
         </is>
       </c>
       <c r="J61" s="2" t="n">
-        <v>411279000</v>
+        <v>314004000</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="n">
-        <v>46230</v>
+        <v>46244</v>
       </c>
       <c r="B62" t="n">
         <v>154</v>
       </c>
-      <c r="C62" s="2" t="n">
-        <v>4044000</v>
-      </c>
-      <c r="D62" s="2" t="n"/>
+      <c r="C62" s="2" t="n"/>
+      <c r="D62" s="2" t="n">
+        <v>9461000</v>
+      </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Bog'ishamol Poligraf MChJ</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>261649818</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>20208000035162662001</t>
+          <t>20208000965261771001</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Оплата за электроэнергию за июль 2026 г.</t>
+          <t>Оплата за продукцию по договору №218/26, НДС 12%</t>
         </is>
       </c>
       <c r="J62" s="2" t="n">
-        <v>407235000</v>
+        <v>323465000</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="n">
-        <v>46230</v>
+        <v>46244</v>
       </c>
       <c r="B63" t="n">
         <v>155</v>
       </c>
-      <c r="C63" s="2" t="n">
-        <v>86103000</v>
-      </c>
-      <c r="D63" s="2" t="n"/>
+      <c r="C63" s="2" t="n"/>
+      <c r="D63" s="2" t="n">
+        <v>7605000</v>
+      </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Sarbon Tikuv MChJ</t>
+          <t>Oltin Vodiy Trans Servis AJ</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>249413941</t>
+          <t>218152313</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>20208000692391483001</t>
+          <t>20208000145679461001</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №17/26</t>
+          <t>Оплата за продукцию по дог. №254/26, НДС 12%</t>
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>321132000</v>
+        <v>331070000</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="n">
-        <v>46231</v>
+        <v>46244</v>
       </c>
       <c r="B64" t="n">
         <v>156</v>
       </c>
-      <c r="C64" s="2" t="n"/>
-      <c r="D64" s="2" t="n">
-        <v>22804000</v>
-      </c>
+      <c r="C64" s="2" t="n">
+        <v>6866000</v>
+      </c>
+      <c r="D64" s="2" t="n"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Angren Meva-Sabzavot MChJ</t>
+          <t>Saodat Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>253616498</t>
+          <t>380705809</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>20208000819652617001</t>
+          <t>20208000721145870001</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №253/26 от 28.07.2026</t>
+          <t>Арендная плата за август 2026 г. по договору №81/24</t>
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>343936000</v>
+        <v>324204000</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="n">
-        <v>46231</v>
+        <v>46244</v>
       </c>
       <c r="B65" t="n">
         <v>157</v>
       </c>
       <c r="C65" s="2" t="n">
-        <v>79645000</v>
+        <v>13953000</v>
       </c>
       <c r="D65" s="2" t="n"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Sarbon Tikuv MChJ</t>
+          <t>Yangi Hayot Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>249413941</t>
+          <t>208026490</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>20208000692391483001</t>
+          <t>20208000194160103001</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №9161</t>
+          <t>Оплата за транспортные услуги по договору №20/26</t>
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>264291000</v>
+        <v>310251000</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="n">
-        <v>46232</v>
+        <v>46245</v>
       </c>
       <c r="B66" t="n">
         <v>158</v>
       </c>
       <c r="C66" s="2" t="n"/>
       <c r="D66" s="2" t="n">
-        <v>5782000</v>
+        <v>13568000</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Angren Meva-Sabzavot MChJ</t>
+          <t>Bog'ishamol Poligraf MChJ</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>253616498</t>
+          <t>261649818</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>20208000819652617001</t>
+          <t>20208000965261771001</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №8533 от 29.07.2026, в т.ч. НДС 12%</t>
+          <t>Оплата по счет-фактуре №1478 за поставленный товар</t>
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>270073000</v>
+        <v>323819000</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="n">
-        <v>46233</v>
+        <v>46245</v>
       </c>
       <c r="B67" t="n">
         <v>159</v>
       </c>
-      <c r="C67" s="2" t="n"/>
-      <c r="D67" s="2" t="n">
-        <v>12803000</v>
-      </c>
+      <c r="C67" s="2" t="n">
+        <v>6406000</v>
+      </c>
+      <c r="D67" s="2" t="n"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Angren Meva-Sabzavot MChJ</t>
+          <t>Yangi Hayot Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>253616498</t>
+          <t>208026490</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>20208000819652617001</t>
+          <t>20208000194160103001</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №7885</t>
+          <t>Оплата за упаковочные материалы, с/ф №8861</t>
         </is>
       </c>
       <c r="J67" s="2" t="n">
-        <v>282876000</v>
+        <v>317413000</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="n">
-        <v>46234</v>
+        <v>46246</v>
       </c>
       <c r="B68" t="n">
         <v>160</v>
       </c>
-      <c r="C68" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D68" s="2" t="n"/>
+      <c r="C68" s="2" t="n"/>
+      <c r="D68" s="2" t="n">
+        <v>11956000</v>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Navbahor Bank ATB</t>
+          <t>Bog'ishamol Poligraf MChJ</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>261649818</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000965261771001</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Плата за SMS-информирование</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №339</t>
         </is>
       </c>
       <c r="J68" s="2" t="n">
-        <v>282576000</v>
+        <v>329369000</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="n">
-        <v>46237</v>
+        <v>46246</v>
       </c>
       <c r="B69" t="n">
         <v>161</v>
       </c>
-      <c r="C69" s="2" t="n"/>
-      <c r="D69" s="2" t="n">
-        <v>182514000</v>
-      </c>
+      <c r="C69" s="2" t="n">
+        <v>35929000</v>
+      </c>
+      <c r="D69" s="2" t="n"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Mehnat Avto Ehtiyot MChJ</t>
+          <t>Namangan Savdo MChJ</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>278183715</t>
+          <t>238865009</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>20208000387539022001</t>
+          <t>20208000683302102001</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №124/26 от 03.08.2026</t>
+          <t>Оплата за упаковочные материалы, с/ф №1522</t>
         </is>
       </c>
       <c r="J69" s="2" t="n">
-        <v>465090000</v>
+        <v>293440000</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="n">
-        <v>46237</v>
+        <v>46247</v>
       </c>
       <c r="B70" t="n">
         <v>162</v>
       </c>
-      <c r="C70" s="2" t="n"/>
-      <c r="D70" s="2" t="n">
-        <v>125206000</v>
-      </c>
+      <c r="C70" s="2" t="n">
+        <v>19985000</v>
+      </c>
+      <c r="D70" s="2" t="n"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Sharq Farm Savdo MChJ</t>
+          <t>Yangi Hayot Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>358401619</t>
+          <t>208026490</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>20208000122270147001</t>
+          <t>20208000194160103001</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3031,472 +3026,477 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №6998 за поставленный товар</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №54/26</t>
         </is>
       </c>
       <c r="J70" s="2" t="n">
-        <v>590296000</v>
+        <v>273455000</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="n">
-        <v>46237</v>
+        <v>46248</v>
       </c>
       <c r="B71" t="n">
         <v>163</v>
       </c>
       <c r="C71" s="2" t="n"/>
       <c r="D71" s="2" t="n">
-        <v>15203000</v>
+        <v>48181000</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Angren Meva-Sabzavot MChJ</t>
+          <t>Bog'ishamol Poligraf MChJ</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>253616498</t>
+          <t>261649818</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>20208000819652617001</t>
+          <t>20208000965261771001</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №2920 от 03.08.2026, в т.ч. НДС 12%</t>
+          <t>Shartnoma №256/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J71" s="2" t="n">
-        <v>605499000</v>
+        <v>321636000</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="n">
-        <v>46237</v>
+        <v>46248</v>
       </c>
       <c r="B72" t="n">
         <v>164</v>
       </c>
-      <c r="C72" s="2" t="n">
-        <v>23652000</v>
-      </c>
-      <c r="D72" s="2" t="n"/>
+      <c r="C72" s="2" t="n"/>
+      <c r="D72" s="2" t="n">
+        <v>35390000</v>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Sarbon Tikuv MChJ</t>
+          <t>Ziyo Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>249413941</t>
+          <t>340161921</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>20208000692391483001</t>
+          <t>20208000227014773001</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №89/26, QQS bilan</t>
+          <t>Оплата по с/ф №7522 за поставленый товар</t>
         </is>
       </c>
       <c r="J72" s="2" t="n">
-        <v>581847000</v>
+        <v>357026000</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="n">
-        <v>46238</v>
+        <v>46251</v>
       </c>
       <c r="B73" t="n">
         <v>165</v>
       </c>
       <c r="C73" s="2" t="n"/>
       <c r="D73" s="2" t="n">
-        <v>18040000</v>
+        <v>35412000</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Xiva Meva-Sabzavot MChJ</t>
+          <t>Bog'ishamol Poligraf MChJ</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>361080264</t>
+          <t>261649818</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>20208000031941601001</t>
+          <t>20208000965261771001</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №9840 за поставленный товар</t>
+          <t>Оплата за продукцию по договору №34/26, НДС 12%</t>
         </is>
       </c>
       <c r="J73" s="2" t="n">
-        <v>599887000</v>
+        <v>392438000</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="n">
-        <v>46238</v>
+        <v>46251</v>
       </c>
       <c r="B74" t="n">
         <v>166</v>
       </c>
       <c r="C74" s="2" t="n"/>
       <c r="D74" s="2" t="n">
-        <v>15869000</v>
+        <v>8751000</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Angren Meva-Sabzavot MChJ</t>
+          <t>Bog'ishamol Poligraf MChJ</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>253616498</t>
+          <t>261649818</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>20208000819652617001</t>
+          <t>20208000965261771001</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>YETKZILGAN TOVAR UCHUN TO'LOV H/F №5030</t>
+          <t>Предоплата за товар по договору №118/26 от 17.08.2026</t>
         </is>
       </c>
       <c r="J74" s="2" t="n">
-        <v>615756000</v>
+        <v>401189000</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="n">
-        <v>46238</v>
+        <v>46251</v>
       </c>
       <c r="B75" t="n">
         <v>167</v>
       </c>
       <c r="C75" s="2" t="n"/>
       <c r="D75" s="2" t="n">
-        <v>9447000</v>
+        <v>6337000</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Angren Meva-Sabzavot MChJ</t>
+          <t>Bog'ishamol Poligraf MChJ</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>253616498</t>
+          <t>261649818</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>20208000819652617001</t>
+          <t>20208000965261771001</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №36/26 от 04.08.2026</t>
+          <t>Оплата по счет-фактуре №4634 за поставленный товар</t>
         </is>
       </c>
       <c r="J75" s="2" t="n">
-        <v>625203000</v>
+        <v>407526000</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="n">
-        <v>46238</v>
+        <v>46251</v>
       </c>
       <c r="B76" t="n">
         <v>168</v>
       </c>
       <c r="C76" s="2" t="n">
-        <v>64816000</v>
+        <v>8839000</v>
       </c>
       <c r="D76" s="2" t="n"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Navbahor Bank ATB</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Перечисление заработной платы за июль 2026 г. согласно реестру №7925</t>
+          <t>Социальный налог за июль 2026 г.</t>
         </is>
       </c>
       <c r="J76" s="2" t="n">
-        <v>560387000</v>
+        <v>398687000</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="n">
-        <v>46240</v>
+        <v>46251</v>
       </c>
       <c r="B77" t="n">
         <v>169</v>
       </c>
-      <c r="C77" s="2" t="n"/>
-      <c r="D77" s="2" t="n">
-        <v>67865000</v>
-      </c>
+      <c r="C77" s="2" t="n">
+        <v>8839000</v>
+      </c>
+      <c r="D77" s="2" t="n"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Sharq Farm Savdo MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>358401619</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>20208000122270147001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ТОВАР ПО СЧЕТ-ФАКТУРЕ №2048 ОТ 06.08.2026, В Т.Ч. НДС 12%</t>
+          <t>Налог на доходы физических лиц за июль 2026 г.</t>
         </is>
       </c>
       <c r="J77" s="2" t="n">
-        <v>628252000</v>
+        <v>389848000</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="n">
-        <v>46240</v>
+        <v>46251</v>
       </c>
       <c r="B78" t="n">
         <v>170</v>
       </c>
-      <c r="C78" s="2" t="n"/>
-      <c r="D78" s="2" t="n">
-        <v>15937000</v>
-      </c>
+      <c r="C78" s="2" t="n">
+        <v>33715000</v>
+      </c>
+      <c r="D78" s="2" t="n"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Mehnat Avto Ehtiyot MChJ</t>
+          <t>Yangi Hayot Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>278183715</t>
+          <t>208026490</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>20208000387539022001</t>
+          <t>20208000194160103001</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №6983 за поставленный товар</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №211/26</t>
         </is>
       </c>
       <c r="J78" s="2" t="n">
-        <v>644189000</v>
+        <v>356133000</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="n">
-        <v>46240</v>
+        <v>46252</v>
       </c>
       <c r="B79" t="n">
         <v>171</v>
       </c>
-      <c r="C79" s="2" t="n">
-        <v>156888000</v>
-      </c>
-      <c r="D79" s="2" t="n"/>
+      <c r="C79" s="2" t="n"/>
+      <c r="D79" s="2" t="n">
+        <v>76689000</v>
+      </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Sarbon Tikuv MChJ</t>
+          <t>Bog'ishamol Poligraf MChJ</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>249413941</t>
+          <t>261649818</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>20208000692391483001</t>
+          <t>20208000965261771001</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по дог. №1/26</t>
+          <t>Оплата за продукцию по договору №48/26, НДС 12%</t>
         </is>
       </c>
       <c r="J79" s="2" t="n">
-        <v>487301000</v>
+        <v>432822000</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="n">
-        <v>46241</v>
+        <v>46252</v>
       </c>
       <c r="B80" t="n">
         <v>172</v>
       </c>
-      <c r="C80" s="2" t="n">
-        <v>6866000</v>
-      </c>
-      <c r="D80" s="2" t="n"/>
+      <c r="C80" s="2" t="n"/>
+      <c r="D80" s="2" t="n">
+        <v>5909000</v>
+      </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Yulduz Qurilish MChJ</t>
+          <t>Bog'ishamol Poligraf MChJ</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>324719468</t>
+          <t>261649818</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>20208000817375960001</t>
+          <t>20208000965261771001</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Арендная плата за август 2026 г. по договору №32/22</t>
+          <t>Оплата за продукцию по договору №176/26, НДС 12%</t>
         </is>
       </c>
       <c r="J80" s="2" t="n">
-        <v>480435000</v>
+        <v>438731000</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="n">
-        <v>46241</v>
+        <v>46253</v>
       </c>
       <c r="B81" t="n">
         <v>173</v>
       </c>
-      <c r="C81" s="2" t="n">
-        <v>157938000</v>
-      </c>
-      <c r="D81" s="2" t="n"/>
+      <c r="C81" s="2" t="n"/>
+      <c r="D81" s="2" t="n">
+        <v>10944000</v>
+      </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Zafar Plastik MChJ</t>
+          <t>Farovon Agro Servis MChJ</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>233388650</t>
+          <t>320702587</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>20208000926833021001</t>
+          <t>20208000053391993001</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №7453</t>
+          <t>Оплата по счет-фактуре №4910 за поставленный товар</t>
         </is>
       </c>
       <c r="J81" s="2" t="n">
-        <v>322497000</v>
+        <v>449675000</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="n">
-        <v>46244</v>
+        <v>46253</v>
       </c>
       <c r="B82" t="n">
         <v>174</v>
       </c>
-      <c r="C82" s="2" t="n"/>
-      <c r="D82" s="2" t="n">
-        <v>46016000</v>
-      </c>
+      <c r="C82" s="2" t="n">
+        <v>15056000</v>
+      </c>
+      <c r="D82" s="2" t="n"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Saodat Mehmonxona MChJ</t>
+          <t>Yangi Hayot Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>391181523</t>
+          <t>208026490</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>20208000341456794001</t>
+          <t>20208000194160103001</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -3506,37 +3506,37 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №8394 10.08.2026, QQS bilan</t>
+          <t>Оплата за товары согласно счет-фактуре №6523</t>
         </is>
       </c>
       <c r="J82" s="2" t="n">
-        <v>368513000</v>
+        <v>434619000</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="n">
-        <v>46244</v>
+        <v>46254</v>
       </c>
       <c r="B83" t="n">
         <v>175</v>
       </c>
       <c r="C83" s="2" t="n"/>
       <c r="D83" s="2" t="n">
-        <v>26183000</v>
+        <v>106572000</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Sharq Farm Savdo MChJ</t>
+          <t>Bog'ishamol Poligraf MChJ</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>358401619</t>
+          <t>261649818</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>20208000122270147001</t>
+          <t>20208000965261771001</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -3546,117 +3546,117 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №6407 за поставленный товар</t>
+          <t>Оплата за товар по счет-фактуре №2003 от 20.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J83" s="2" t="n">
-        <v>394696000</v>
+        <v>541191000</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="n">
-        <v>46244</v>
+        <v>46254</v>
       </c>
       <c r="B84" t="n">
         <v>176</v>
       </c>
       <c r="C84" s="2" t="n"/>
       <c r="D84" s="2" t="n">
-        <v>18155000</v>
+        <v>51024000</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Angren Meva-Sabzavot MChJ</t>
+          <t>Nihol Non MChJ</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>253616498</t>
+          <t>365496405</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>20208000819652617001</t>
+          <t>20208000922502059001</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №7964 за поставленный товар</t>
+          <t>Shartnoma №218/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J84" s="2" t="n">
-        <v>412851000</v>
+        <v>592215000</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="n">
-        <v>46244</v>
+        <v>46254</v>
       </c>
       <c r="B85" t="n">
         <v>177</v>
       </c>
       <c r="C85" s="2" t="n"/>
       <c r="D85" s="2" t="n">
-        <v>14645000</v>
+        <v>6183000</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Zafar Trans Servis MChJ</t>
+          <t>Ziyo Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>217207025</t>
+          <t>340161921</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>20208000750533919001</t>
+          <t>20208000227014773001</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №143/26 от 10.08.2026</t>
+          <t>Оплата по счет-фактуре №50 за поставленный товар</t>
         </is>
       </c>
       <c r="J85" s="2" t="n">
-        <v>427496000</v>
+        <v>598398000</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="n">
-        <v>46244</v>
+        <v>46255</v>
       </c>
       <c r="B86" t="n">
         <v>178</v>
       </c>
       <c r="C86" s="2" t="n"/>
       <c r="D86" s="2" t="n">
-        <v>8847000</v>
+        <v>54405000</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Mehnat Avto Ehtiyot MChJ</t>
+          <t>Farovon Agro Servis MChJ</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>278183715</t>
+          <t>320702587</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>20208000387539022001</t>
+          <t>20208000053391993001</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -3666,237 +3666,237 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №126/26 от 10.08.2026</t>
+          <t>Оплата по счет-фактуре №7218 за поставленный товар</t>
         </is>
       </c>
       <c r="J86" s="2" t="n">
-        <v>436343000</v>
+        <v>652803000</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="n">
-        <v>46244</v>
+        <v>46255</v>
       </c>
       <c r="B87" t="n">
         <v>179</v>
       </c>
-      <c r="C87" s="2" t="n">
-        <v>22159000</v>
-      </c>
-      <c r="D87" s="2" t="n"/>
+      <c r="C87" s="2" t="n"/>
+      <c r="D87" s="2" t="n">
+        <v>24940000</v>
+      </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Sarbon Tikuv MChJ</t>
+          <t>Bog'ishamol Poligraf MChJ</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>249413941</t>
+          <t>261649818</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>20208000692391483001</t>
+          <t>20208000965261771001</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №5205</t>
+          <t>Оплата за товар по счет-фактуре №7606 от 21.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J87" s="2" t="n">
-        <v>414184000</v>
+        <v>677743000</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="n">
-        <v>46245</v>
+        <v>46255</v>
       </c>
       <c r="B88" t="n">
         <v>180</v>
       </c>
-      <c r="C88" s="2" t="n"/>
-      <c r="D88" s="2" t="n">
-        <v>24006000</v>
-      </c>
+      <c r="C88" s="2" t="n">
+        <v>11322000</v>
+      </c>
+      <c r="D88" s="2" t="n"/>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Angren Meva-Sabzavot MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>253616498</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>20208000819652617001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №4221 от 11.08.2026, в т.ч. НДС 12%</t>
+          <t>НДС за июль 2026 г.</t>
         </is>
       </c>
       <c r="J88" s="2" t="n">
-        <v>438190000</v>
+        <v>666421000</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="n">
-        <v>46245</v>
+        <v>46258</v>
       </c>
       <c r="B89" t="n">
         <v>181</v>
       </c>
       <c r="C89" s="2" t="n"/>
       <c r="D89" s="2" t="n">
-        <v>8877000</v>
+        <v>26637000</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Angren Meva-Sabzavot MChJ</t>
+          <t>Ziyo Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>253616498</t>
+          <t>340161921</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>20208000819652617001</t>
+          <t>20208000227014773001</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №266/26, НДС 12%</t>
+          <t>Mahsulot uchun to'lov, shartn. №115/26, QQS 12%</t>
         </is>
       </c>
       <c r="J89" s="2" t="n">
-        <v>447067000</v>
+        <v>693058000</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="n">
-        <v>46246</v>
+        <v>46258</v>
       </c>
       <c r="B90" t="n">
         <v>182</v>
       </c>
-      <c r="C90" s="2" t="n">
-        <v>16133000</v>
-      </c>
-      <c r="D90" s="2" t="n"/>
+      <c r="C90" s="2" t="n"/>
+      <c r="D90" s="2" t="n">
+        <v>8663000</v>
+      </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Sarbon Tikuv MChJ</t>
+          <t>Bog'ishamol Poligraf MChJ</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>249413941</t>
+          <t>261649818</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>20208000692391483001</t>
+          <t>20208000965261771001</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №3469</t>
+          <t>Предоплата за товар по договору №110/26 от 24.08.2026</t>
         </is>
       </c>
       <c r="J90" s="2" t="n">
-        <v>430934000</v>
+        <v>701721000</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="n">
-        <v>46247</v>
+        <v>46258</v>
       </c>
       <c r="B91" t="n">
         <v>183</v>
       </c>
-      <c r="C91" s="2" t="n"/>
-      <c r="D91" s="2" t="n">
-        <v>13833000</v>
-      </c>
+      <c r="C91" s="2" t="n">
+        <v>6600000</v>
+      </c>
+      <c r="D91" s="2" t="n"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Saodat Mehmonxona MChJ</t>
+          <t>Farg'ona Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>391181523</t>
+          <t>341394196</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>20208000341456794001</t>
+          <t>20208000239148343001</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №219/26, НДС 12%</t>
+          <t>Оплата за транспортные услуги по договору №4/26</t>
         </is>
       </c>
       <c r="J91" s="2" t="n">
-        <v>444767000</v>
+        <v>695121000</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="n">
-        <v>46248</v>
+        <v>46258</v>
       </c>
       <c r="B92" t="n">
         <v>184</v>
       </c>
-      <c r="C92" s="2" t="n"/>
-      <c r="D92" s="2" t="n">
-        <v>16837000</v>
-      </c>
+      <c r="C92" s="2" t="n">
+        <v>31266000</v>
+      </c>
+      <c r="D92" s="2" t="n"/>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Sharq Farm Savdo MChJ</t>
+          <t>Namangan Savdo MChJ</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>358401619</t>
+          <t>238865009</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>20208000122270147001</t>
+          <t>20208000683302102001</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -3906,277 +3906,272 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №5893 от 14.08.2026, в т.ч. НДС 12%</t>
+          <t>Предоплата за материалы по договору №231/26</t>
         </is>
       </c>
       <c r="J92" s="2" t="n">
-        <v>461604000</v>
+        <v>663855000</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="n">
-        <v>46251</v>
+        <v>46259</v>
       </c>
       <c r="B93" t="n">
         <v>185</v>
       </c>
       <c r="C93" s="2" t="n"/>
       <c r="D93" s="2" t="n">
-        <v>21818000</v>
+        <v>33136000</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Qarshi Qog'oz AJ</t>
+          <t>Bog'ishamol Poligraf MChJ</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>268883284</t>
+          <t>261649818</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>20208000822335239001</t>
+          <t>20208000965261771001</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №230/26 от 17.08.2026</t>
+          <t>Оплата за продукцию по договору №293/26, НДС 12%</t>
         </is>
       </c>
       <c r="J93" s="2" t="n">
-        <v>483422000</v>
+        <v>696991000</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="n">
-        <v>46251</v>
+        <v>46259</v>
       </c>
       <c r="B94" t="n">
         <v>186</v>
       </c>
       <c r="C94" s="2" t="n"/>
       <c r="D94" s="2" t="n">
-        <v>12177000</v>
+        <v>21913000</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Xiva Meva-Sabzavot MChJ</t>
+          <t>Bog'ishamol Poligraf MChJ</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>361080264</t>
+          <t>261649818</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>20208000031941601001</t>
+          <t>20208000965261771001</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Shartnoma №202/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата по счет-фактуре №6160 за поставленный товар</t>
         </is>
       </c>
       <c r="J94" s="2" t="n">
-        <v>495599000</v>
+        <v>718904000</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="n">
-        <v>46251</v>
+        <v>46259</v>
       </c>
       <c r="B95" t="n">
         <v>187</v>
       </c>
       <c r="C95" s="2" t="n">
-        <v>8839000</v>
+        <v>44100000</v>
       </c>
       <c r="D95" s="2" t="n"/>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>201122905</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2024-8374)</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>16307000381312376417</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Ijtimoiy soliq iyul 2026</t>
+          <t>Kredit shartnomasi L-2024-8374 bo'yicha navbatdagi to'lov (08.2026)</t>
         </is>
       </c>
       <c r="J95" s="2" t="n">
-        <v>486760000</v>
+        <v>674804000</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="n">
-        <v>46251</v>
+        <v>46260</v>
       </c>
       <c r="B96" t="n">
         <v>188</v>
       </c>
-      <c r="C96" s="2" t="n">
-        <v>8839000</v>
-      </c>
-      <c r="D96" s="2" t="n"/>
+      <c r="C96" s="2" t="n"/>
+      <c r="D96" s="2" t="n">
+        <v>15089000</v>
+      </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Ziyo Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>340161921</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000227014773001</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Налог на доходы физических лиц за июль 2026 г.</t>
+          <t>Предоплата за товар по дог. №281/26 от 26.08.2026</t>
         </is>
       </c>
       <c r="J96" s="2" t="n">
-        <v>477921000</v>
+        <v>689893000</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="n">
-        <v>46251</v>
+        <v>46260</v>
       </c>
       <c r="B97" t="n">
         <v>189</v>
       </c>
-      <c r="C97" s="2" t="n">
-        <v>24609000</v>
-      </c>
-      <c r="D97" s="2" t="n"/>
+      <c r="C97" s="2" t="n"/>
+      <c r="D97" s="2" t="n">
+        <v>11719000</v>
+      </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Sarbon Tikuv MChJ</t>
+          <t>Bog'ishamol Poligraf MChJ</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>249413941</t>
+          <t>261649818</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>20208000692391483001</t>
+          <t>20208000965261771001</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №75/26</t>
+          <t>Оплата за товар по счет-фактуре №4195 от 26.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J97" s="2" t="n">
-        <v>453312000</v>
+        <v>701612000</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="n">
-        <v>46251</v>
+        <v>46260</v>
       </c>
       <c r="B98" t="n">
         <v>190</v>
       </c>
       <c r="C98" s="2" t="n">
-        <v>115157000</v>
+        <v>275514000</v>
       </c>
       <c r="D98" s="2" t="n"/>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Zafar Plastik MChJ</t>
+          <t>Yangi Hayot Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>233388650</t>
+          <t>208026490</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>20208000926833021001</t>
+          <t>20208000194160103001</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ТРАНСПОРТНЫЕ УСЛУГИ ПО ДОГОВОРУ №113/26</t>
+          <t>Оплата за упаковочные материалы, с/ф №1361</t>
         </is>
       </c>
       <c r="J98" s="2" t="n">
-        <v>338155000</v>
+        <v>426098000</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="n">
-        <v>46252</v>
+        <v>46261</v>
       </c>
       <c r="B99" t="n">
         <v>191</v>
       </c>
       <c r="C99" s="2" t="n"/>
       <c r="D99" s="2" t="n">
-        <v>13989000</v>
+        <v>43725000</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Sharq Farm Savdo MChJ</t>
+          <t>Bog'ishamol Poligraf MChJ</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>358401619</t>
+          <t>261649818</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>20208000122270147001</t>
+          <t>20208000965261771001</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -4186,157 +4181,157 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №7901 за поставленный товар</t>
+          <t>Оплата за продукцию по договору №171/26, НДС 12%</t>
         </is>
       </c>
       <c r="J99" s="2" t="n">
-        <v>352144000</v>
+        <v>469823000</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="n">
-        <v>46252</v>
+        <v>46261</v>
       </c>
       <c r="B100" t="n">
         <v>192</v>
       </c>
-      <c r="C100" s="2" t="n">
-        <v>35156000</v>
-      </c>
-      <c r="D100" s="2" t="n"/>
+      <c r="C100" s="2" t="n"/>
+      <c r="D100" s="2" t="n">
+        <v>15103000</v>
+      </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Sarbon Tikuv MChJ</t>
+          <t>Bog'ishamol Poligraf MChJ</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>249413941</t>
+          <t>261649818</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>20208000692391483001</t>
+          <t>20208000965261771001</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по дог. №240/26</t>
+          <t>Оплата за товар по счет-фактуре №1296 от 27.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J100" s="2" t="n">
-        <v>316988000</v>
+        <v>484926000</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="n">
-        <v>46252</v>
+        <v>46261</v>
       </c>
       <c r="B101" t="n">
         <v>193</v>
       </c>
       <c r="C101" s="2" t="n">
-        <v>44561000</v>
+        <v>4291000</v>
       </c>
       <c r="D101" s="2" t="n"/>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Gulshan Qurilish MChJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>261605721</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>20208000392064893001</t>
+          <t>20208000165844298001</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №108/26</t>
+          <t>Elektr energiyasi uchun to'lov avgust</t>
         </is>
       </c>
       <c r="J101" s="2" t="n">
-        <v>272427000</v>
+        <v>480635000</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="n">
-        <v>46253</v>
+        <v>46261</v>
       </c>
       <c r="B102" t="n">
         <v>194</v>
       </c>
       <c r="C102" s="2" t="n">
-        <v>14715000</v>
+        <v>9967000</v>
       </c>
       <c r="D102" s="2" t="n"/>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Durdona Mebel AJ</t>
+          <t>Omad Logistik AJ</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>246657965</t>
+          <t>205736713</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>20208000591929530001</t>
+          <t>20208000255022933001</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №6884</t>
+          <t>Оплата за сырье по договору №54/26 от 27.08.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J102" s="2" t="n">
-        <v>257712000</v>
+        <v>470668000</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="n">
-        <v>46253</v>
+        <v>46262</v>
       </c>
       <c r="B103" t="n">
         <v>195</v>
       </c>
       <c r="C103" s="2" t="n">
-        <v>15425000</v>
+        <v>147203000</v>
       </c>
       <c r="D103" s="2" t="n"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Andijon Un Mahsulotlari MChJ</t>
+          <t>Yangi Hayot Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>291057367</t>
+          <t>208026490</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>20208000362550229001</t>
+          <t>20208000194160103001</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -4346,37 +4341,32 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №1548</t>
+          <t>Оплата за транспортные услуги по дог. №266/26</t>
         </is>
       </c>
       <c r="J103" s="2" t="n">
-        <v>242287000</v>
+        <v>323465000</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="n">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="B104" t="n">
         <v>196</v>
       </c>
-      <c r="C104" s="2" t="n"/>
-      <c r="D104" s="2" t="n">
-        <v>15304000</v>
-      </c>
+      <c r="C104" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D104" s="2" t="n"/>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Angren Meva-Sabzavot MChJ</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>253616498</t>
+          <t>Navbahor Bank ATB</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>20208000819652617001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -4386,117 +4376,117 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>ОПЛАТА ПО СЧЕТ-ФАКТУРЕ №3519 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
+          <t>ПЛАТА ЗА SMS-ИНФОРМИРОВАНИЕ</t>
         </is>
       </c>
       <c r="J104" s="2" t="n">
-        <v>257591000</v>
+        <v>323165000</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="n">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="B105" t="n">
         <v>197</v>
       </c>
-      <c r="C105" s="2" t="n"/>
-      <c r="D105" s="2" t="n">
-        <v>8916000</v>
-      </c>
+      <c r="C105" s="2" t="n">
+        <v>6945000</v>
+      </c>
+      <c r="D105" s="2" t="n"/>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Angren Meva-Sabzavot MChJ</t>
+          <t>Bekobod Plastik MChJ</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>253616498</t>
+          <t>319468781</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>20208000819652617001</t>
+          <t>20208000375960103001</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №137/26 от 24.08.2026</t>
+          <t>Оплата за сырье по договору №154/26 от 31.08.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J105" s="2" t="n">
-        <v>266507000</v>
+        <v>316220000</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="n">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="B106" t="n">
         <v>198</v>
       </c>
       <c r="C106" s="2" t="n">
-        <v>11112000</v>
+        <v>52624000</v>
       </c>
       <c r="D106" s="2" t="n"/>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Bekobod Savdo MChJ</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>365796585</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000192953032001</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>НДС за июль 2026 г.</t>
+          <t>Оплата за транспортные услуги по договору №39/26</t>
         </is>
       </c>
       <c r="J106" s="2" t="n">
-        <v>255395000</v>
+        <v>263596000</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="n">
-        <v>46258</v>
+        <v>46266</v>
       </c>
       <c r="B107" t="n">
         <v>199</v>
       </c>
       <c r="C107" s="2" t="n">
-        <v>16153000</v>
+        <v>13597000</v>
       </c>
       <c r="D107" s="2" t="n"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Sarbon Tikuv MChJ</t>
+          <t>Nurafshon Yog'och AJ</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>249413941</t>
+          <t>328909975</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>20208000692391483001</t>
+          <t>20208000034535471001</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -4506,77 +4496,72 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №8920</t>
+          <t>Оплата за товары согласно с/ф №3552</t>
         </is>
       </c>
       <c r="J107" s="2" t="n">
-        <v>239242000</v>
+        <v>249999000</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="n">
-        <v>46258</v>
+        <v>46269</v>
       </c>
       <c r="B108" t="n">
         <v>200</v>
       </c>
-      <c r="C108" s="2" t="n">
-        <v>57450000</v>
-      </c>
-      <c r="D108" s="2" t="n"/>
+      <c r="C108" s="2" t="n"/>
+      <c r="D108" s="2" t="n">
+        <v>36311000</v>
+      </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Sarbon Tikuv MChJ</t>
+          <t>Ziyo Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>249413941</t>
+          <t>340161921</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>20208000692391483001</t>
+          <t>20208000227014773001</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №125/26 от 24.08.2026, НДС 12%</t>
+          <t>Tovar uchun to'lov, hisob-faktura №4796 04.09.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J108" s="2" t="n">
-        <v>181792000</v>
+        <v>286310000</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="n">
-        <v>46259</v>
+        <v>46269</v>
       </c>
       <c r="B109" t="n">
         <v>201</v>
       </c>
-      <c r="C109" s="2" t="n"/>
-      <c r="D109" s="2" t="n">
-        <v>29860000</v>
-      </c>
+      <c r="C109" s="2" t="n">
+        <v>62765000</v>
+      </c>
+      <c r="D109" s="2" t="n"/>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Angren Meva-Sabzavot MChJ</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>253616498</t>
+          <t>Navbahor Bank ATB</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>20208000819652617001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -4586,192 +4571,197 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №3100 25.08.2026, QQS bilan</t>
+          <t>Заработная плата за август 2026 г. (перечисление на пастиковые карты)</t>
         </is>
       </c>
       <c r="J109" s="2" t="n">
-        <v>211652000</v>
+        <v>223545000</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="3" t="n">
-        <v>46259</v>
+        <v>46272</v>
       </c>
       <c r="B110" t="n">
         <v>202</v>
       </c>
-      <c r="C110" s="2" t="n">
-        <v>4291000</v>
-      </c>
-      <c r="D110" s="2" t="n"/>
+      <c r="C110" s="2" t="n"/>
+      <c r="D110" s="2" t="n">
+        <v>42367000</v>
+      </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Afrosiyob Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>352915466</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>20208000035162662001</t>
+          <t>20208000699589126001</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Оплата за электроэнергию согласно счету</t>
+          <t>Оплата за товар по с/ф №575 от 07.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J110" s="2" t="n">
-        <v>207361000</v>
+        <v>265912000</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="3" t="n">
-        <v>46259</v>
+        <v>46272</v>
       </c>
       <c r="B111" t="n">
         <v>203</v>
       </c>
-      <c r="C111" s="2" t="n">
-        <v>15120000</v>
-      </c>
-      <c r="D111" s="2" t="n"/>
+      <c r="C111" s="2" t="n"/>
+      <c r="D111" s="2" t="n">
+        <v>13309000</v>
+      </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Durdona Mebel AJ</t>
+          <t>Ziyo Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>246657965</t>
+          <t>340161921</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>20208000591929530001</t>
+          <t>20208000227014773001</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №46/26 от 25.08.2026, НДС 12%</t>
+          <t>Оплата по счет-фактуре №8619 за поставленный товар</t>
         </is>
       </c>
       <c r="J111" s="2" t="n">
-        <v>192241000</v>
+        <v>279221000</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="3" t="n">
-        <v>46259</v>
+        <v>46273</v>
       </c>
       <c r="B112" t="n">
         <v>204</v>
       </c>
       <c r="C112" s="2" t="n">
-        <v>44100000</v>
+        <v>6649000</v>
       </c>
       <c r="D112" s="2" t="n"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2024-8374)</t>
+          <t>Saodat Qurilish Materiallari MChJ</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>380705809</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>16307000381312376417</t>
+          <t>20208000721145870001</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2024-8374 bo'yicha navbatdagi to'lov (08.2026)</t>
+          <t>Аренда помещения за сентябрь, дог. №81/24</t>
         </is>
       </c>
       <c r="J112" s="2" t="n">
-        <v>148141000</v>
+        <v>272572000</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="3" t="n">
-        <v>46260</v>
+        <v>46274</v>
       </c>
       <c r="B113" t="n">
         <v>205</v>
       </c>
       <c r="C113" s="2" t="n"/>
       <c r="D113" s="2" t="n">
-        <v>125922000</v>
+        <v>254267000</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Angren Meva-Sabzavot MChJ</t>
+          <t>Nihol Plastik XK</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>253616498</t>
+          <t>318371553</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>20208000819652617001</t>
+          <t>20208000753902296001</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №162/26 от 26.08.2026</t>
+          <t>Shartnoma №56/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J113" s="2" t="n">
-        <v>274063000</v>
+        <v>526839000</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="3" t="n">
-        <v>46260</v>
+        <v>46274</v>
       </c>
       <c r="B114" t="n">
         <v>206</v>
       </c>
-      <c r="C114" s="2" t="n"/>
-      <c r="D114" s="2" t="n">
-        <v>20513000</v>
-      </c>
+      <c r="C114" s="2" t="n">
+        <v>66175000</v>
+      </c>
+      <c r="D114" s="2" t="n"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Saodat Mehmonxona MChJ</t>
+          <t>Yangi Hayot Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>391181523</t>
+          <t>208026490</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>20208000341456794001</t>
+          <t>20208000194160103001</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -4781,37 +4771,37 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №5691 за поставленный товар</t>
+          <t>Tovarlar uchun to'lov h/f №8114</t>
         </is>
       </c>
       <c r="J114" s="2" t="n">
-        <v>294576000</v>
+        <v>460664000</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="3" t="n">
-        <v>46260</v>
+        <v>46274</v>
       </c>
       <c r="B115" t="n">
         <v>207</v>
       </c>
       <c r="C115" s="2" t="n">
-        <v>20382000</v>
+        <v>71214000</v>
       </c>
       <c r="D115" s="2" t="n"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Andijon Un Mahsulotlari MChJ</t>
+          <t>Yangi Hayot Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>291057367</t>
+          <t>208026490</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>20208000362550229001</t>
+          <t>20208000194160103001</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -4821,37 +4811,37 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №9627</t>
+          <t>Оплата за сырье по договору №217/26 от 09.09.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J115" s="2" t="n">
-        <v>274194000</v>
+        <v>389450000</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="3" t="n">
-        <v>46260</v>
+        <v>46276</v>
       </c>
       <c r="B116" t="n">
         <v>208</v>
       </c>
       <c r="C116" s="2" t="n">
-        <v>49507000</v>
+        <v>18669000</v>
       </c>
       <c r="D116" s="2" t="n"/>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Andijon Un Mahsulotlari MChJ</t>
+          <t>Yangi Hayot Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>291057367</t>
+          <t>208026490</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>20208000362550229001</t>
+          <t>20208000194160103001</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -4861,547 +4851,557 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №1180</t>
+          <t>Оплата за товары согласно счет-фактуре №3934</t>
         </is>
       </c>
       <c r="J116" s="2" t="n">
-        <v>224687000</v>
+        <v>370781000</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="3" t="n">
-        <v>46261</v>
+        <v>46279</v>
       </c>
       <c r="B117" t="n">
         <v>209</v>
       </c>
-      <c r="C117" s="2" t="n">
-        <v>17006000</v>
-      </c>
-      <c r="D117" s="2" t="n"/>
+      <c r="C117" s="2" t="n"/>
+      <c r="D117" s="2" t="n">
+        <v>43455000</v>
+      </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Sarbon Tikuv MChJ</t>
+          <t>Ziyo Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>249413941</t>
+          <t>340161921</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>20208000692391483001</t>
+          <t>20208000227014773001</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ТОВАРЫ СОГЛАСНО С/Ф №399</t>
+          <t>Оплата за товар по счет-фактуре №9042 от 14.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J117" s="2" t="n">
-        <v>207681000</v>
+        <v>414236000</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="3" t="n">
-        <v>46262</v>
+        <v>46279</v>
       </c>
       <c r="B118" t="n">
         <v>210</v>
       </c>
-      <c r="C118" s="2" t="n"/>
-      <c r="D118" s="2" t="n">
-        <v>27618000</v>
-      </c>
+      <c r="C118" s="2" t="n">
+        <v>11768000</v>
+      </c>
+      <c r="D118" s="2" t="n"/>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Mehnat Avto Ehtiyot MChJ</t>
+          <t>Bahor Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>278183715</t>
+          <t>283745177</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>20208000387539022001</t>
+          <t>20208000157261107001</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №58/26 от 28.08.2026</t>
+          <t>Предоплата за материалы по договору №265/26</t>
         </is>
       </c>
       <c r="J118" s="2" t="n">
-        <v>235299000</v>
+        <v>402468000</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="3" t="n">
-        <v>46262</v>
+        <v>46279</v>
       </c>
       <c r="B119" t="n">
         <v>211</v>
       </c>
-      <c r="C119" s="2" t="n"/>
-      <c r="D119" s="2" t="n">
-        <v>22407000</v>
-      </c>
+      <c r="C119" s="2" t="n">
+        <v>37928000</v>
+      </c>
+      <c r="D119" s="2" t="n"/>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Nukus Oziq-ovqat Savdo MChJ</t>
+          <t>Yangi Hayot Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>316189013</t>
+          <t>208026490</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>20208000860801121001</t>
+          <t>20208000194160103001</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №2964 за поставленный товар</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №251/26, QQS bilan</t>
         </is>
       </c>
       <c r="J119" s="2" t="n">
-        <v>257706000</v>
+        <v>364540000</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="3" t="n">
-        <v>46265</v>
+        <v>46279</v>
       </c>
       <c r="B120" t="n">
         <v>212</v>
       </c>
       <c r="C120" s="2" t="n">
-        <v>300000</v>
+        <v>59754000</v>
       </c>
       <c r="D120" s="2" t="n"/>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Navbahor Bank ATB</t>
+          <t>Yangi Hayot Qog'oz MChJ</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>208026490</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000194160103001</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Плата за SMS-информирование</t>
+          <t>Оплата за сырье по договору №81/26 от 14.09.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J120" s="2" t="n">
-        <v>257406000</v>
+        <v>304786000</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="3" t="n">
-        <v>46266</v>
+        <v>46280</v>
       </c>
       <c r="B121" t="n">
         <v>213</v>
       </c>
-      <c r="C121" s="2" t="n"/>
-      <c r="D121" s="2" t="n">
-        <v>9997000</v>
-      </c>
+      <c r="C121" s="2" t="n">
+        <v>8559000</v>
+      </c>
+      <c r="D121" s="2" t="n"/>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Angren Meva-Sabzavot MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>253616498</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>20208000819652617001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №88/26 от 01.09.2026</t>
+          <t>Социальный налог за август 2026 г.</t>
         </is>
       </c>
       <c r="J121" s="2" t="n">
-        <v>267403000</v>
+        <v>296227000</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="3" t="n">
-        <v>46267</v>
+        <v>46280</v>
       </c>
       <c r="B122" t="n">
         <v>214</v>
       </c>
-      <c r="C122" s="2" t="n"/>
-      <c r="D122" s="2" t="n">
-        <v>40533000</v>
-      </c>
+      <c r="C122" s="2" t="n">
+        <v>8559000</v>
+      </c>
+      <c r="D122" s="2" t="n"/>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Angren Meva-Sabzavot MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>253616498</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>20208000819652617001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №255/26, НДС 12%</t>
+          <t>JShDS avgust oyi uchun</t>
         </is>
       </c>
       <c r="J122" s="2" t="n">
-        <v>307936000</v>
+        <v>287668000</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="3" t="n">
-        <v>46268</v>
+        <v>46281</v>
       </c>
       <c r="B123" t="n">
         <v>215</v>
       </c>
       <c r="C123" s="2" t="n"/>
       <c r="D123" s="2" t="n">
-        <v>15471000</v>
+        <v>16091000</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Angren Meva-Sabzavot MChJ</t>
+          <t>Bog'ishamol Poligraf MChJ</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>253616498</t>
+          <t>261649818</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>20208000819652617001</t>
+          <t>20208000965261771001</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №6728 за поставленный товар</t>
+          <t>Предоплата за товар по договору №137/26 от 16.09.2026</t>
         </is>
       </c>
       <c r="J123" s="2" t="n">
-        <v>323407000</v>
+        <v>303759000</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="3" t="n">
-        <v>46268</v>
+        <v>46281</v>
       </c>
       <c r="B124" t="n">
         <v>216</v>
       </c>
-      <c r="C124" s="2" t="n">
-        <v>40850000</v>
-      </c>
-      <c r="D124" s="2" t="n"/>
+      <c r="C124" s="2" t="n"/>
+      <c r="D124" s="2" t="n">
+        <v>12846000</v>
+      </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Sarbon Tikuv MChJ</t>
+          <t>Lazzat Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>249413941</t>
+          <t>308416312</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>20208000692391483001</t>
+          <t>20208000505130127001</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №1917</t>
+          <t>Оплата за продукцию по дог. №145/26, НДС 12%</t>
         </is>
       </c>
       <c r="J124" s="2" t="n">
-        <v>282557000</v>
+        <v>316605000</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="3" t="n">
-        <v>46269</v>
+        <v>46281</v>
       </c>
       <c r="B125" t="n">
         <v>217</v>
       </c>
       <c r="C125" s="2" t="n">
-        <v>133567000</v>
+        <v>23618000</v>
       </c>
       <c r="D125" s="2" t="n"/>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Zafar Plastik MChJ</t>
+          <t>Farg'ona Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>233388650</t>
+          <t>341394196</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>20208000926833021001</t>
+          <t>20208000239148343001</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ТОВАРЫ СОГЛАСНО С/Ф №173</t>
+          <t>Оплата за товары согласно с/ф №1948</t>
         </is>
       </c>
       <c r="J125" s="2" t="n">
-        <v>148990000</v>
+        <v>292987000</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="3" t="n">
-        <v>46272</v>
+        <v>46282</v>
       </c>
       <c r="B126" t="n">
         <v>218</v>
       </c>
       <c r="C126" s="2" t="n"/>
       <c r="D126" s="2" t="n">
-        <v>55400000</v>
+        <v>39971000</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Angren Meva-Sabzavot MChJ</t>
+          <t>Bog'ishamol Poligraf MChJ</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>253616498</t>
+          <t>261649818</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>20208000819652617001</t>
+          <t>20208000965261771001</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №5505 от 07.09.2026, в т.ч. НДС 12%</t>
+          <t>Предоплата за товар по дог. №270/26 от 17.09.2026</t>
         </is>
       </c>
       <c r="J126" s="2" t="n">
-        <v>204390000</v>
+        <v>332958000</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="3" t="n">
-        <v>46272</v>
+        <v>46282</v>
       </c>
       <c r="B127" t="n">
         <v>219</v>
       </c>
       <c r="C127" s="2" t="n"/>
       <c r="D127" s="2" t="n">
-        <v>12586000</v>
+        <v>15793000</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Angren Meva-Sabzavot MChJ</t>
+          <t>Bog'ishamol Poligraf MChJ</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>253616498</t>
+          <t>261649818</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>20208000819652617001</t>
+          <t>20208000965261771001</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дг. №259/26, НДС 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №6046</t>
         </is>
       </c>
       <c r="J127" s="2" t="n">
-        <v>216976000</v>
+        <v>348751000</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="3" t="n">
-        <v>46272</v>
+        <v>46283</v>
       </c>
       <c r="B128" t="n">
         <v>220</v>
       </c>
       <c r="C128" s="2" t="n">
-        <v>62765000</v>
+        <v>12175000</v>
       </c>
       <c r="D128" s="2" t="n"/>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Navbahor Bank ATB</t>
+          <t>Namangan Savdo MChJ</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>238865009</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000683302102001</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Заработная плата за август 2026 г. (перечисление на пластиковые карты)</t>
+          <t>Оплата за упаковочные материалы, с/ф №8675</t>
         </is>
       </c>
       <c r="J128" s="2" t="n">
-        <v>154211000</v>
+        <v>336576000</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="3" t="n">
-        <v>46272</v>
+        <v>46286</v>
       </c>
       <c r="B129" t="n">
         <v>221</v>
       </c>
-      <c r="C129" s="2" t="n">
-        <v>68131000</v>
-      </c>
-      <c r="D129" s="2" t="n"/>
+      <c r="C129" s="2" t="n"/>
+      <c r="D129" s="2" t="n">
+        <v>252955000</v>
+      </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Durdona Mebel AJ</t>
+          <t>Bog'ishamol Poligraf MChJ</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>246657965</t>
+          <t>261649818</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>20208000591929530001</t>
+          <t>20208000965261771001</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №174/26</t>
+          <t>Предоплата за товар по дог. №283/26 от 21.09.2026</t>
         </is>
       </c>
       <c r="J129" s="2" t="n">
-        <v>86080000</v>
+        <v>589531000</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="3" t="n">
-        <v>46274</v>
+        <v>46286</v>
       </c>
       <c r="B130" t="n">
         <v>222</v>
       </c>
-      <c r="C130" s="2" t="n">
-        <v>6649000</v>
-      </c>
-      <c r="D130" s="2" t="n"/>
+      <c r="C130" s="2" t="n"/>
+      <c r="D130" s="2" t="n">
+        <v>47071000</v>
+      </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Yulduz Qurilish MChJ</t>
+          <t>Nihol Plastik XK</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>324719468</t>
+          <t>318371553</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>20208000817375960001</t>
+          <t>20208000753902296001</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -5411,37 +5411,37 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Bino ijarasi uchun to'lov sentyabr</t>
+          <t>Оплата за продукцию по договору №33/26, НДС 12%</t>
         </is>
       </c>
       <c r="J130" s="2" t="n">
-        <v>79431000</v>
+        <v>636602000</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="3" t="n">
-        <v>46275</v>
+        <v>46286</v>
       </c>
       <c r="B131" t="n">
         <v>223</v>
       </c>
-      <c r="C131" s="2" t="n">
-        <v>40422000</v>
-      </c>
-      <c r="D131" s="2" t="n"/>
+      <c r="C131" s="2" t="n"/>
+      <c r="D131" s="2" t="n">
+        <v>32558000</v>
+      </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Andijon Un Mahsulotlari MChJ</t>
+          <t>Ziyo Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>291057367</t>
+          <t>340161921</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>20208000362550229001</t>
+          <t>20208000227014773001</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -5451,222 +5451,222 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Оплата за сырье по дог. №273/26 от 10.09.2026, НДС 12%</t>
+          <t>Оплата по счет-фактуре №3886 за поставленный товар</t>
         </is>
       </c>
       <c r="J131" s="2" t="n">
-        <v>39009000</v>
+        <v>669160000</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="3" t="n">
-        <v>46276</v>
+        <v>46286</v>
       </c>
       <c r="B132" t="n">
         <v>224</v>
       </c>
       <c r="C132" s="2" t="n"/>
       <c r="D132" s="2" t="n">
-        <v>304714000</v>
+        <v>21916000</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Angren Meva-Sabzavot MChJ</t>
+          <t>Nihol Non MChJ</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>253616498</t>
+          <t>365496405</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>20208000819652617001</t>
+          <t>20208000922502059001</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №3820 от 11.09.2026, в т.ч. НДС 12%</t>
+          <t>Предоплата за товар по договору №250/26 от 21.09.2026</t>
         </is>
       </c>
       <c r="J132" s="2" t="n">
-        <v>343723000</v>
+        <v>691076000</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="3" t="n">
-        <v>46279</v>
+        <v>46286</v>
       </c>
       <c r="B133" t="n">
         <v>225</v>
       </c>
-      <c r="C133" s="2" t="n">
-        <v>20420000</v>
-      </c>
-      <c r="D133" s="2" t="n"/>
+      <c r="C133" s="2" t="n"/>
+      <c r="D133" s="2" t="n">
+        <v>17699000</v>
+      </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Sarbon Tikuv MChJ</t>
+          <t>Ziyo Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>249413941</t>
+          <t>340161921</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>20208000692391483001</t>
+          <t>20208000227014773001</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные маериалы, с/ф №2175</t>
+          <t>Оплата за продукцию по договору №227/26, НДС 12%</t>
         </is>
       </c>
       <c r="J133" s="2" t="n">
-        <v>323303000</v>
+        <v>708775000</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="3" t="n">
-        <v>46279</v>
+        <v>46286</v>
       </c>
       <c r="B134" t="n">
         <v>226</v>
       </c>
       <c r="C134" s="2" t="n">
-        <v>55267000</v>
+        <v>30890000</v>
       </c>
       <c r="D134" s="2" t="n"/>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Zafar Plastik MChJ</t>
+          <t>Yangi Hayot Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>233388650</t>
+          <t>208026490</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>20208000926833021001</t>
+          <t>20208000194160103001</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №191/26</t>
+          <t>Предоплата за материалы по договору №34/26</t>
         </is>
       </c>
       <c r="J134" s="2" t="n">
-        <v>268036000</v>
+        <v>677885000</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="3" t="n">
-        <v>46280</v>
+        <v>46286</v>
       </c>
       <c r="B135" t="n">
         <v>227</v>
       </c>
-      <c r="C135" s="2" t="n"/>
-      <c r="D135" s="2" t="n">
-        <v>14935000</v>
-      </c>
+      <c r="C135" s="2" t="n">
+        <v>149199000</v>
+      </c>
+      <c r="D135" s="2" t="n"/>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Sharq Farm Savdo MChJ</t>
+          <t>Barakali Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>358401619</t>
+          <t>362648128</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>20208000122270147001</t>
+          <t>20208000970161843001</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №181/26 от 15.09.2026</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №58/26</t>
         </is>
       </c>
       <c r="J135" s="2" t="n">
-        <v>282971000</v>
+        <v>528686000</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="3" t="n">
-        <v>46280</v>
+        <v>46287</v>
       </c>
       <c r="B136" t="n">
         <v>228</v>
       </c>
       <c r="C136" s="2" t="n"/>
       <c r="D136" s="2" t="n">
-        <v>10630000</v>
+        <v>28750000</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Andijon Sut Mahsulotlari MChJ</t>
+          <t>Farovon Agro Servis MChJ</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>348084163</t>
+          <t>320702587</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>20208000245051301001</t>
+          <t>20208000053391993001</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №162/26, НДС 12%</t>
+          <t>Mahsulot uchun to'lov, shartnoma №292/26, QQS 12%</t>
         </is>
       </c>
       <c r="J136" s="2" t="n">
-        <v>293601000</v>
+        <v>557436000</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="3" t="n">
-        <v>46280</v>
+        <v>46287</v>
       </c>
       <c r="B137" t="n">
         <v>229</v>
       </c>
       <c r="C137" s="2" t="n">
-        <v>8559000</v>
+        <v>11222000</v>
       </c>
       <c r="D137" s="2" t="n"/>
       <c r="E137" t="inlineStr">
@@ -5691,117 +5691,117 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>УПЛАТА СОЦИАЛЬНОГО НАЛОГА ЗА АВГУСТ</t>
+          <t>Qo'shilgan qiymat solig'i avgust oyi</t>
         </is>
       </c>
       <c r="J137" s="2" t="n">
-        <v>285042000</v>
+        <v>546214000</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="3" t="n">
-        <v>46280</v>
+        <v>46288</v>
       </c>
       <c r="B138" t="n">
         <v>230</v>
       </c>
-      <c r="C138" s="2" t="n">
-        <v>8559000</v>
-      </c>
-      <c r="D138" s="2" t="n"/>
+      <c r="C138" s="2" t="n"/>
+      <c r="D138" s="2" t="n">
+        <v>21788000</v>
+      </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Bog'ishamol Poligraf MChJ</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>261649818</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000965261771001</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Налог на доходы физических лиц за август 2026 г.</t>
+          <t>Предоплата за товар по договору №21/26 от 23.09.2026</t>
         </is>
       </c>
       <c r="J138" s="2" t="n">
-        <v>276483000</v>
+        <v>568002000</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="3" t="n">
-        <v>46280</v>
+        <v>46288</v>
       </c>
       <c r="B139" t="n">
         <v>231</v>
       </c>
       <c r="C139" s="2" t="n">
-        <v>54815000</v>
+        <v>24779000</v>
       </c>
       <c r="D139" s="2" t="n"/>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Sarbon Tikuv MChJ</t>
+          <t>Yangi Hayot Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>249413941</t>
+          <t>208026490</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>20208000692391483001</t>
+          <t>20208000194160103001</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №4459</t>
+          <t>Оплата за товары согласно счет-фактуре №1281</t>
         </is>
       </c>
       <c r="J139" s="2" t="n">
-        <v>221668000</v>
+        <v>543223000</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="3" t="n">
-        <v>46281</v>
+        <v>46289</v>
       </c>
       <c r="B140" t="n">
         <v>232</v>
       </c>
-      <c r="C140" s="2" t="n"/>
-      <c r="D140" s="2" t="n">
-        <v>52785000</v>
-      </c>
+      <c r="C140" s="2" t="n">
+        <v>76698000</v>
+      </c>
+      <c r="D140" s="2" t="n"/>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Xiva Meva-Sabzavot MChJ</t>
+          <t>Farg'ona Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>361080264</t>
+          <t>341394196</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>20208000031941601001</t>
+          <t>20208000239148343001</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -5811,986 +5811,266 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №6121 от 16.09.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за сырье по дог. №8/26 от 24.09.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J140" s="2" t="n">
-        <v>274453000</v>
+        <v>466525000</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="3" t="n">
-        <v>46281</v>
+        <v>46290</v>
       </c>
       <c r="B141" t="n">
         <v>233</v>
       </c>
-      <c r="C141" s="2" t="n"/>
-      <c r="D141" s="2" t="n">
-        <v>21503000</v>
-      </c>
+      <c r="C141" s="2" t="n">
+        <v>4156000</v>
+      </c>
+      <c r="D141" s="2" t="n"/>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Sharq Farm Savdo MChJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>358401619</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>20208000122270147001</t>
+          <t>20208000165844298001</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №1221</t>
+          <t>ОПЛАТА ЗА ЭЛЕКТРОЭНЕРГИЮ ЗА СЕНТЯБРЬ 2026 Г.</t>
         </is>
       </c>
       <c r="J141" s="2" t="n">
-        <v>295956000</v>
+        <v>462369000</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="3" t="n">
-        <v>46281</v>
+        <v>46290</v>
       </c>
       <c r="B142" t="n">
         <v>234</v>
       </c>
-      <c r="C142" s="2" t="n"/>
-      <c r="D142" s="2" t="n">
-        <v>14484000</v>
-      </c>
+      <c r="C142" s="2" t="n">
+        <v>15673000</v>
+      </c>
+      <c r="D142" s="2" t="n"/>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Saodat Mehmonxona MChJ</t>
+          <t>Nurafshon Yog'och AJ</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>391181523</t>
+          <t>328909975</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>20208000341456794001</t>
+          <t>20208000034535471001</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №253/26 от 1.09.2026</t>
+          <t>Materiallar uchun oldindan to'lov, shartn. №99/26</t>
         </is>
       </c>
       <c r="J142" s="2" t="n">
-        <v>310440000</v>
+        <v>446696000</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="3" t="n">
-        <v>46281</v>
+        <v>46290</v>
       </c>
       <c r="B143" t="n">
         <v>235</v>
       </c>
-      <c r="C143" s="2" t="n"/>
-      <c r="D143" s="2" t="n">
-        <v>12942000</v>
-      </c>
+      <c r="C143" s="2" t="n">
+        <v>44100000</v>
+      </c>
+      <c r="D143" s="2" t="n"/>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Jizzax Mehmonxona MChJ</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>249529154</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2024-8374)</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>20208000626995891001</t>
+          <t>16307000381312376417</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №1638</t>
+          <t>Kredit shartnomasi L-2024-8374 bo'yicha navbatdagi to'lov (09.2026)</t>
         </is>
       </c>
       <c r="J143" s="2" t="n">
-        <v>323382000</v>
+        <v>402596000</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="3" t="n">
-        <v>46282</v>
+        <v>46293</v>
       </c>
       <c r="B144" t="n">
         <v>236</v>
       </c>
-      <c r="C144" s="2" t="n"/>
-      <c r="D144" s="2" t="n">
-        <v>14774000</v>
-      </c>
+      <c r="C144" s="2" t="n">
+        <v>190495000</v>
+      </c>
+      <c r="D144" s="2" t="n"/>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Qarshi Qog'oz AJ</t>
+          <t>Yangi Hayot Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>268883284</t>
+          <t>208026490</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>20208000822335239001</t>
+          <t>20208000194160103001</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №286/26 от 17.09.2026</t>
+          <t>Предплата за материалы по договору №106/26</t>
         </is>
       </c>
       <c r="J144" s="2" t="n">
-        <v>338156000</v>
+        <v>212101000</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="3" t="n">
-        <v>46283</v>
+        <v>46295</v>
       </c>
       <c r="B145" t="n">
         <v>237</v>
       </c>
-      <c r="C145" s="2" t="n">
-        <v>16856000</v>
-      </c>
-      <c r="D145" s="2" t="n"/>
+      <c r="C145" s="2" t="n"/>
+      <c r="D145" s="2" t="n">
+        <v>37999000</v>
+      </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Sarbon Tikuv MChJ</t>
+          <t>Shahrisabz Farm Savdo XK</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>249413941</t>
+          <t>388328458</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>20208000692391483001</t>
+          <t>20208000233523997001</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №73/26, QQS bilan</t>
+          <t>Предоплата за товар по договору №140/26 от 30.09.2026</t>
         </is>
       </c>
       <c r="J145" s="2" t="n">
-        <v>321300000</v>
+        <v>250100000</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="3" t="n">
-        <v>46283</v>
+        <v>46295</v>
       </c>
       <c r="B146" t="n">
         <v>238</v>
       </c>
       <c r="C146" s="2" t="n">
-        <v>51498000</v>
+        <v>300000</v>
       </c>
       <c r="D146" s="2" t="n"/>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Sarbon Tikuv MChJ</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>249413941</t>
+          <t>Navbahor Bank ATB</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>20208000692391483001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №189/26</t>
+          <t>Плата за SMS-информирование</t>
         </is>
       </c>
       <c r="J146" s="2" t="n">
-        <v>269802000</v>
+        <v>249800000</v>
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="3" t="n">
-        <v>46286</v>
-      </c>
-      <c r="B147" t="n">
-        <v>239</v>
-      </c>
-      <c r="C147" s="2" t="n"/>
-      <c r="D147" s="2" t="n">
-        <v>53836000</v>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>Angren Meva-Sabzavot MChJ</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>253616498</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>20208000819652617001</t>
-        </is>
-      </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>01121</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГОВОРУ №101/26, НДС 12%</t>
-        </is>
-      </c>
-      <c r="J147" s="2" t="n">
-        <v>323638000</v>
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Итого обороты:</t>
+        </is>
+      </c>
+      <c r="C147" s="4" t="n">
+        <v>2812935000</v>
+      </c>
+      <c r="D147" s="4" t="n">
+        <v>2780835000</v>
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="3" t="n">
-        <v>46286</v>
-      </c>
-      <c r="B148" t="n">
-        <v>240</v>
-      </c>
-      <c r="C148" s="2" t="n"/>
-      <c r="D148" s="2" t="n">
-        <v>46176000</v>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>Angren Meva-Sabzavot MChJ</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>253616498</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>20208000819652617001</t>
-        </is>
-      </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>01121</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr">
-        <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №2042</t>
-        </is>
-      </c>
-      <c r="J148" s="2" t="n">
-        <v>369814000</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="3" t="n">
-        <v>46286</v>
-      </c>
-      <c r="B149" t="n">
-        <v>241</v>
-      </c>
-      <c r="C149" s="2" t="n"/>
-      <c r="D149" s="2" t="n">
-        <v>15038000</v>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>Zafar Trans Servis MChJ</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>217207025</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>20208000750533919001</t>
-        </is>
-      </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>Shartnoma №167/26 bo'yicha oldindan to'lov</t>
-        </is>
-      </c>
-      <c r="J149" s="2" t="n">
-        <v>384852000</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="3" t="n">
-        <v>46286</v>
-      </c>
-      <c r="B150" t="n">
-        <v>242</v>
-      </c>
-      <c r="C150" s="2" t="n"/>
-      <c r="D150" s="2" t="n">
-        <v>9541000</v>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>Angren Meva-Sabzavot MChJ</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>253616498</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>20208000819652617001</t>
-        </is>
-      </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>01121</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>Mahsulot uchun to'lov, shartnoma №125/26, QQS 12%</t>
-        </is>
-      </c>
-      <c r="J150" s="2" t="n">
-        <v>394393000</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" s="3" t="n">
-        <v>46286</v>
-      </c>
-      <c r="B151" t="n">
-        <v>243</v>
-      </c>
-      <c r="C151" s="2" t="n">
-        <v>24308000</v>
-      </c>
-      <c r="D151" s="2" t="n"/>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>Sarbon Tikuv MChJ</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>249413941</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>20208000692391483001</t>
-        </is>
-      </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t>Предоплата за материалы по договору №124/26</t>
-        </is>
-      </c>
-      <c r="J151" s="2" t="n">
-        <v>370085000</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="3" t="n">
-        <v>46286</v>
-      </c>
-      <c r="B152" t="n">
-        <v>244</v>
-      </c>
-      <c r="C152" s="2" t="n">
-        <v>63941000</v>
-      </c>
-      <c r="D152" s="2" t="n"/>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>Sarbon Tikuv MChJ</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>249413941</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>20208000692391483001</t>
-        </is>
-      </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I152" t="inlineStr">
-        <is>
-          <t>Оплата за товары согласно счет-фактуре №7067</t>
-        </is>
-      </c>
-      <c r="J152" s="2" t="n">
-        <v>306144000</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="3" t="n">
-        <v>46287</v>
-      </c>
-      <c r="B153" t="n">
-        <v>245</v>
-      </c>
-      <c r="C153" s="2" t="n"/>
-      <c r="D153" s="2" t="n">
-        <v>34431000</v>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>Angren Meva-Sabzavot MChJ</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>253616498</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>20208000819652617001</t>
-        </is>
-      </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>01121</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr">
-        <is>
-          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГОВОРУ №252/26, НДС 12%</t>
-        </is>
-      </c>
-      <c r="J153" s="2" t="n">
-        <v>340575000</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="3" t="n">
-        <v>46287</v>
-      </c>
-      <c r="B154" t="n">
-        <v>246</v>
-      </c>
-      <c r="C154" s="2" t="n">
-        <v>11234000</v>
-      </c>
-      <c r="D154" s="2" t="n"/>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>201122905</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>23402000300100001010</t>
-        </is>
-      </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>00014</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr">
-        <is>
-          <t>НДС за август 2026 г.</t>
-        </is>
-      </c>
-      <c r="J154" s="2" t="n">
-        <v>329341000</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="3" t="n">
-        <v>46287</v>
-      </c>
-      <c r="B155" t="n">
-        <v>247</v>
-      </c>
-      <c r="C155" s="2" t="n">
-        <v>210450000</v>
-      </c>
-      <c r="D155" s="2" t="n"/>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>Gulshan Qurilish MChJ</t>
-        </is>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>261605721</t>
-        </is>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>20208000392064893001</t>
-        </is>
-      </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr">
-        <is>
-          <t>ОПЛАТА ЗА ТОВАРЫ СОГЛАСНО СЧЕТ-ФАКТУРЕ №7241</t>
-        </is>
-      </c>
-      <c r="J155" s="2" t="n">
-        <v>118891000</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="3" t="n">
-        <v>46289</v>
-      </c>
-      <c r="B156" t="n">
-        <v>248</v>
-      </c>
-      <c r="C156" s="2" t="n"/>
-      <c r="D156" s="2" t="n">
-        <v>15249000</v>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>Saodat Mehmonxona MChJ</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>391181523</t>
-        </is>
-      </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>20208000341456794001</t>
-        </is>
-      </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>01153</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>Оплата по счет-фактуре №8197 за поставленный товар</t>
-        </is>
-      </c>
-      <c r="J156" s="2" t="n">
-        <v>134140000</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" s="3" t="n">
-        <v>46289</v>
-      </c>
-      <c r="B157" t="n">
-        <v>249</v>
-      </c>
-      <c r="C157" s="2" t="n"/>
-      <c r="D157" s="2" t="n">
-        <v>8828000</v>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>Angren Meva-Sabzavot MChJ</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>253616498</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>20208000819652617001</t>
-        </is>
-      </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>01121</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>Оплата по счет-фактуре №753 за поставленный товар</t>
-        </is>
-      </c>
-      <c r="J157" s="2" t="n">
-        <v>142968000</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="3" t="n">
-        <v>46290</v>
-      </c>
-      <c r="B158" t="n">
-        <v>250</v>
-      </c>
-      <c r="C158" s="2" t="n"/>
-      <c r="D158" s="2" t="n">
-        <v>16627000</v>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>Zafar Trans Servis MChJ</t>
-        </is>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>217207025</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>20208000750533919001</t>
-        </is>
-      </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t>Оплата за продукцию по договору №24/26, НДС 12%</t>
-        </is>
-      </c>
-      <c r="J158" s="2" t="n">
-        <v>159595000</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" s="3" t="n">
-        <v>46290</v>
-      </c>
-      <c r="B159" t="n">
-        <v>251</v>
-      </c>
-      <c r="C159" s="2" t="n"/>
-      <c r="D159" s="2" t="n">
-        <v>13589000</v>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>Saodat Mehmonxona MChJ</t>
-        </is>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>391181523</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>20208000341456794001</t>
-        </is>
-      </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>01153</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>Оплата за товар по с/ф №3468от 25.09.2026, в т.ч. НДС 12%</t>
-        </is>
-      </c>
-      <c r="J159" s="2" t="n">
-        <v>173184000</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="3" t="n">
-        <v>46290</v>
-      </c>
-      <c r="B160" t="n">
-        <v>252</v>
-      </c>
-      <c r="C160" s="2" t="n">
-        <v>44100000</v>
-      </c>
-      <c r="D160" s="2" t="n"/>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2024-8374)</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>16307000381312376417</t>
-        </is>
-      </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>01121</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr">
-        <is>
-          <t>Kredit shartnomasi L-2024-8374 bo'yicha navbatdagi to'lov (09.2026)</t>
-        </is>
-      </c>
-      <c r="J160" s="2" t="n">
-        <v>129084000</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" s="3" t="n">
-        <v>46293</v>
-      </c>
-      <c r="B161" t="n">
-        <v>253</v>
-      </c>
-      <c r="C161" s="2" t="n"/>
-      <c r="D161" s="2" t="n">
-        <v>142136000</v>
-      </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>Angren Meva-Sabzavot MChJ</t>
-        </is>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>253616498</t>
-        </is>
-      </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>20208000819652617001</t>
-        </is>
-      </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>01121</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr">
-        <is>
-          <t>Оплата за товар по счет-фактуре №1529 от 28.09.2026, в т.ч. НДС 12%</t>
-        </is>
-      </c>
-      <c r="J161" s="2" t="n">
-        <v>271220000</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" s="3" t="n">
-        <v>46293</v>
-      </c>
-      <c r="B162" t="n">
-        <v>254</v>
-      </c>
-      <c r="C162" s="2" t="n">
-        <v>4156000</v>
-      </c>
-      <c r="D162" s="2" t="n"/>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
-        </is>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>200933985</t>
-        </is>
-      </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>20208000035162662001</t>
-        </is>
-      </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>01121</t>
-        </is>
-      </c>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t>Оплата за электроэнергию за сентябрь 2026 г.</t>
-        </is>
-      </c>
-      <c r="J162" s="2" t="n">
-        <v>267064000</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="3" t="n">
-        <v>46293</v>
-      </c>
-      <c r="B163" t="n">
-        <v>255</v>
-      </c>
-      <c r="C163" s="2" t="n">
-        <v>16964000</v>
-      </c>
-      <c r="D163" s="2" t="n"/>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>Andijon Un Mahsulotlari MChJ</t>
-        </is>
-      </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>291057367</t>
-        </is>
-      </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>20208000362550229001</t>
-        </is>
-      </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>01153</t>
-        </is>
-      </c>
-      <c r="I163" t="inlineStr">
-        <is>
-          <t>Предоплата за материалы по договору №202/26</t>
-        </is>
-      </c>
-      <c r="J163" s="2" t="n">
-        <v>250100000</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" s="3" t="n">
-        <v>46295</v>
-      </c>
-      <c r="B164" t="n">
-        <v>256</v>
-      </c>
-      <c r="C164" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D164" s="2" t="n"/>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>Navbahor Bank ATB</t>
-        </is>
-      </c>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>45994000900000001001</t>
-        </is>
-      </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>01121</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr">
-        <is>
-          <t>Комиссия за перевод</t>
-        </is>
-      </c>
-      <c r="J164" s="2" t="n">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Исходящий остаток на 30.09.2026:</t>
+        </is>
+      </c>
+      <c r="C148" s="4" t="n">
         <v>249800000</v>
       </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>Итого обороты:</t>
-        </is>
-      </c>
-      <c r="C165" s="4" t="n">
-        <v>2797535000</v>
-      </c>
-      <c r="D165" s="4" t="n">
-        <v>2765435000</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>Исходящий остаток на 30.09.2026:</t>
-        </is>
-      </c>
-      <c r="C166" s="4" t="n">
-        <v>249800000</v>
-      </c>
-      <c r="D166" s="4" t="n"/>
+      <c r="D148" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
